--- a/outputs/tables/ranking_semantico.xlsx
+++ b/outputs/tables/ranking_semantico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,46 +476,46 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42326244</t>
+          <t>39925031</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>History, Virology, Pathogenesis, Epidemiology, and Laboratory Diagnosis of Dengue Virus: A Focused Review.</t>
+          <t>Cosmeceuticals in the Pediatric Population Part I: A Review of Risks and Available Evidence.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Shinde RV; Mohite ST; Durgawale PP; Patil SR; Shinde AR; Shinde SB</t>
+          <t>Goff GK; Stein SL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cureus</t>
+          <t>Pediatric dermatology</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.7759/cureus.109151</t>
+          <t>10.1111/dth.15903</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Dengue virus (DENV) is a mosquito-borne flavivirus with four antigenically distinct serotypes and represents a leading cause of acute febrile illness in tropical and subtropical regions worldwide. This focused review summarizes the historical evolution of dengue disease descriptions, virus discovery, vectors and transmission dynamics, viral structure, mechanisms of pathogenesis-including antibody-dependent enhancement (ADE) and non-structural protein-1 (NS1)-mediated endothelial dysfunction-clinical classification, current epidemiology with emphasis on India, and laboratory diagnostic approaches. We highlight persistent gaps in molecular surveillance, particularly incomplete genotype and lineage characterization in routine hospital-based studies, and discuss emerging diagnostic and surveillance tools such as real-time reverse transcription polymerase chain reaction (RT-PCR), NS1 antigen detection, isothermal amplification, plaque reduction neutralization tests (PRNT), and genomic sequencing. The review concludes by outlining priorities for strengthening surveillance, diagnostics, and research to improve clinical management, vaccine policy, and public health response in endemic and peri-urban/rural settings.</t>
+          <t>The rise in the use of cosmeceuticals among children and adolescents has created a new challenge for dermatologists, who are confronted with the task of advising young patients on the risks that these products can carry and the often questionable efficacy of these products. While some cosmeceuticals can be beneficial for this population when used correctly, such as broad-spectrum sunscreen or specific anti-acne agents, other products may not carry benefits for young skin and could even cause complications, particularly in young consumers who have skin conditions such as acne or atopic dermatitis. Many of the common ingredients in cosmeceutical products have had very limited (if any) studies conducted in pediatric populations, and much of the data regarding the efficacy claims and risks of these products must be inferred from studies in adult patients.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42326244/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39925031/</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.5543</v>
+        <v>0.7655</v>
       </c>
     </row>
     <row r="3">
@@ -526,46 +526,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>42257899</t>
+          <t>38443125</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Clinical characteristics and outcomes of dengue-associated transverse myelitis: A systematic review of case reports.</t>
+          <t>Attenuation of Atopic Dermatitis in Newborns, Infants, and Children With Prescription Treatment and Ceramide-Containing Skin Care: A Systematic Literature Review and Consensus.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Duarte N; Ruiz O; Refaey A</t>
+          <t>Schachner LA; Andriessen A; Benjamin L; Gonzalez ME; Kircik L; Lio P; Micali G</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neurological sciences : official journal of the Italian Neurological Society and of the Italian Society of Clinical Neurophysiology</t>
+          <t>Journal of drugs in dermatology : JDD</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.1007/s11910-022-01213-7</t>
+          <t>10.36849/jdd.7894</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Dengue is a globally prevalent arboviral infection with an expanding spectrum of recognized neurological complications. Dengue-associated transverse myelitis (DATM) is a rare but potentially disabling manifestation, and its clinical characteristics and outcomes have not been systematically synthesized. Characterize the level and extent of spinal cord involvement, clinical presentation, management, and outcomes of DATM. A systematic review was conducted in accordance with PRISMA 2020 guidelines. PubMed, Scopus, Embase (Ovid), and Web of Science were searched from inception through October 2025. Case reports describing transverse myelitis in patients with confirmed dengue infection were included. Data were extracted and synthesized descriptively. Methodological quality was assessed using the Joanna Briggs Institute (JBI) Checklist for Case Reports. Twenty-nine case reports met inclusion criteria. The median age was 38 (IQR 20) years, with male predominance (62.1%). Neurological symptoms developed a median of 6 (IQR 4) days after dengue onset. Urinary retention (79.3%) and paraparesis (69.0%) were the most common presenting features, and a thoracic sensory level was frequently identified (65.5%). Spinal MRI most often demonstrated longitudinally extensive transverse myelitis (65.5%). Corticosteroids were administered in 82.8% of cases. At discharge, 69% had partial recovery and 17.2% complete recovery. Mortality was low (3.4%; one case). DATM is a rare, early-onset neurological complication of dengue characterized by urinary retention, paraparesis, and frequent thoracic cord involvement, often with longitudinally extensive lesions on MRI. Although most patients experience partial or complete recovery, residual deficits may occur. Evidence is limited to case reports, precluding estimation of incidence or comparative treatment efficacy. Early recognition and exclusion of alternative causes of acute myelopathy are essential.</t>
+          <t>Atopic dermatitis (AD) typically starts in infancy and early childhood. The chronic skin disorder is associated with recurrent flares, pruritus, and genetic predisposition. Daily use of moisturizers that contain lipids, such as ceramides, reduces the rate of AD flares and the need for topical steroid treatment. We aimed to provide insights on AD attenuation to tailor AD prescription therapy, skin care, and maintenance treatment to improve pediatric patients with AD and families. A panel of 6 pediatric dermatologists and dermatologists who treat neonates, infants, and children developed a consensus paper on AD attenuation for pediatric patients. The modified Delphi process comprised a face-to-face panel meeting and online follow-up to discuss the systematic literature search results and draw from clinical experience and opinion of the panel to adopt and agree on 5 statements.&amp;nbsp; Results: Understanding the functional properties of newborn and infant skin, discussing skincare product use with parents, and recommending tailored prescription and skincare routines can improve newborn, infant, and children&amp;rsquo;s skin health. Studies on the prophylactic application of moisturizers initiated in early infancy suggest moisturizers may delay rather than prevent AD, especially in high-risk populations and when used continuously. Increasingly there is evidence that moisturizer application reduces the severity of AD and extends the time to flares, which may help attenuate the atopic march. The protective effect of skin care for AD has been observed in studies where its daily use is ongoing; these beneficial effects may be lost in less than 1year after cessation. It is therefore important to emphasize that skin care should be routinely used when counseling patients and caregivers.&amp;nbsp; Conclusion: Healthcare providers can improve patient outcomes in atopic-prone infants and children by providing instructions regarding the daily benefits of applying skin care with gentle cleansers and moisturizers. Using gentle cleansers and moisturizers containing barrier lipids from birth onward may delay AD occurrence and mitigate severity in predisposed infants.J Drugs Dermatol. 2024;23(3): doi:10.36849/JDD.7894.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42257899/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/38443125/</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.554</v>
+        <v>0.7163</v>
       </c>
     </row>
     <row r="4">
@@ -576,46 +576,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>42338893</t>
+          <t>30303557</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Assessing the burden of diabetes mellitus in dengue patients: A systematic review and meta-analysis.</t>
+          <t>A comparison of international management guidelines for atopic dermatitis.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lin J; Navarra A; Vita S; D'Abramo A; Faraglia F; Tomassi MV; De Marco P; Nicastri E</t>
+          <t>LePoidevin LM; Lee DE; Shi VY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>New microbes and new infections</t>
+          <t>Pediatric dermatology</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.1016/j.jinf.2026.106707</t>
+          <t>10.1111/pde.13678</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Dengue is a rapidly expanding mosquito-borne viral disease and a growing global public health challenge. Simultaneously, the prevalence of diabetes mellitus (DM) continues to rise worldwide. DM, often referred to as a silent pandemic, is characterized by chronic inflammation, endothelial dysfunction, and impaired immune responses, mechanisms that may worsen dengue outcomes. Given this context, our study aimed to systematically synthesize evidence on the association between DM and severe dengue outcomes, especially severe dengue and dengue-related mortality. PubMed, Scopus, and Embase were searched, alongside manual screening of reference lists, for English-language observational studies published between 1987 and 2025 reporting dengue outcomes in patients with and without DM. Severe dengue definitions based on both WHO 1997 and WHO 2009 classifications were considered. Screening, data extraction, and risk-of-bias assessment were performed independently by two reviewers, with disagreements resolved by consensus. Pooled odds ratios (ORs) with 95% confidence intervals (CIs) were estimated using random-effects models. A total of 27 eligible studies involving 734,123 participants met the inclusion criteria. Compared with non-diabetic patients, those with DM had significantly higher odds of severe dengue (OR: 2.66, 95% CI: 1.90-3.73) and of dengue-related mortality (OR: 3.95, 95% CI: 2.98-5.23). DM is independently associated with severe dengue and dengue-related mortality. These findings underscore the need for early identification and close monitoring of diabetic patients in dengue-endemic settings, and for integrated management strategies addressing both infectious and non-communicable diseases. Further research is needed to elucidate the underlying mechanisms and evaluate targeted interventions in this vulnerable population.</t>
+          <t>Atopic dermatitis (AD) is a chronic condition that is predominantly found in pediatric patients and commonly presents therapeutic challenges. The management of AD encompasses a variety of factors, and the pillars of optimal management revolve around skin barrier repair and antiinflammatory, antimicrobial, and antipruritic treatment. AD management guidelines exist in various geographic regions globally. The purpose of this review was to compare international guidelines to highlight the similarities and variances among populations and skin types. Comparisons were made for recommendations regarding moisturization, bathing, wet wrap therapy, topical corticosteroids, topical calcineurin inhibitors, antihistamines, antipruritics, antibiotics, systemic immunosuppressants, and biologics. A literature search of the PubMed, EMBASE, and MEDLINE databases was performed for published guidelines in each geographic region. Inclusion criteria included publications available in English that were established by a dermatological association or group including dermatologists, pertained to the treatment of AD in humans, were the most recent guidelines available that were published between 2007 and 2018, and included comprehensive treatment recommendations. Publications from Europe, North America, Asia, the Asia-Pacific region, Australia, and Africa were reviewed, encompassing 14 guidelines. Notable diversity exists across these guidelines regarding recommendations for moisturization and bathing, as well as topical and systemic therapies for AD. Due to the heterogeneity of the disease and regional treatment accessibility, complete standardization of AD management guidelines may be difficult. Nevertheless, more consensus on management guidelines is needed, and recommendations should be updated as new treatment modalities become available.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42338893/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/30303557/</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.5538</v>
+        <v>0.7155</v>
       </c>
     </row>
     <row r="5">
@@ -626,17 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>42309463</t>
+          <t>41949508</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Clinical Spectrum, neuroimaging, treatment, and outcomes of dengue-associated spinal cord involvement.</t>
+          <t>Guidelines of care for the management of atopic dermatitis in pediatric patients.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Garg RK; Singh R; Paliwal VK; Singhal S</t>
+          <t>Davis DMR; Alikhan A; Bercovitch L; Cohen DE; Darr JM; Drucker AM; Eichenfield LF; Frazer-Green L; Paller AS; Schwarzenberger K; Silverberg JI; Singh AM; Wu PA; Sidbury R</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,26 +646,26 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infectious diseases now</t>
+          <t>Journal of the American Academy of Dermatology</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.1016/j.idnow.2026.105301</t>
+          <t>10.1016/j.jaad.2026.02.113</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Dengue-associated spinal cord involvement is an uncommon but clinically important neurological complication of dengue infection. Existing evidence is fragmented and largely limited to isolated case reports, case series, and small observational studies. This systematic review evaluated the clinical spectrum, neuroimaging findings, pathogenesis, treatment approaches, and outcomes of dengue-associated spinal cord involvement. A systematic review was conducted according to PRISMA 2020 guidelines. PubMed, Embase, Scopus, and Google Scholar were searched from inception to the final search date. Case reports, case series, and cohort studies describing spinal cord involvement associated with dengue infection were included. A total of 85 individual cases and 13 cohort studies were analyzed. Acute transverse myelitis (24/85, 28%) and longitudinally extensive transverse myelitis (22/85, 26%) were the most common syndromes, while hemorrhagic or compressive spinal cord syndromes accounted for 18/85 (21%). Neurological manifestations developed during the acute or parainfectious phase in 46/85 (54%) and during the postinfectious phase in 35/85 (41%). Long-segment spinal cord lesions were identified in 34/85 (40%), and hemorrhagic spinal lesions in 21/85 (25%). Brain or cranial nerve involvement accompanied spinal disease in 35/85 (41%). Intravenous corticosteroids were administered in 53/85 (62%) patients. Complete or near-complete neurological recovery occurred in 39/85 (46%), whereas persistent severe disability occurred in 11/85 (13%). Cohort studies confirmed that dengue-associated myelitis is rare but clinically significant. Dengue-associated spinal cord disease represents a heterogeneous neuro-immunological spectrum requiring early recognition and timely management.</t>
+          <t>Pediatric atopic dermatitis (AD) is a common, chronic inflammatory skin disorder that significantly impacts the quality of life of affected children and their families. Multiple therapies were approved to treat AD in children and adolescents since publication of the AAD's 2014 AD guidelines. To provide evidence-based recommendations on the use of topical therapies, phototherapy, and systemic therapies for AD in children and adolescents. A multidisciplinary workgroup conducted a systematic review and applied the GRADE approach for assessing the certainty of evidence and formulating and grading recommendations. The workgroup developed 27 evidence-based recommendations on the medical management of pediatric AD. This analysis is based on the best available evidence at the time it was conducted. Most randomized controlled trials of therapies for AD are of short duration limiting long-term efficacy and safety conclusions. We make strong recommendations for the use of moisturizers, topical calcineurin inhibitors, topical corticosteroids, crisaborole ointment, roflumilast cream, ruxolitinib cream, tapinarof cream, dupilumab, tralokinumab, lebrikizumab, nemolizumab with concomitant topical therapy, upadacitinib, abrocitinib, and baricitinib in the treatment of pediatric AD. We make conditional recommendations in favor of bathing, bleach baths, wet dressings, phototherapy, methotrexate, mycophenolate mofetil, azathioprine, and cyclosporine. We conditionally recommend against the use of topical antimicrobials, PUVA phototherapy, and strongly recommend against systemic corticosteroids.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42309463/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41949508/</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.547</v>
+        <v>0.7127</v>
       </c>
     </row>
     <row r="6">
@@ -676,46 +676,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>42357692</t>
+          <t>40097336</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Determinants of Dengue Serotype Shifts: A Narrative Multifactorial Perspective.</t>
+          <t>Evidence-Based Recommendations for Managing Atopic Dermatitis in Pediatric Patients: A Systematic Review and Meta-Analysis From the Pediatric Dermatology Special Interest Group of IADVL.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Suppiah J; Rajendiran S; Rashid SA; Ab Hamid N; Zulkifli MMS; Mohd Zain R</t>
+          <t>Mahajan R; Sarkar R; Panda M; Katakam BK; Padhiyar J; Haritha T; Mohapatra L; Patro N; Vora R; Shah S; Gaurkar SP; Patel KB; Rangappa V</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Viruses</t>
+          <t>International journal of dermatology</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10.4269/ajtmh.2008.79.128</t>
+          <t>10.1111/ijd.17723</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Dengue Virus (DENV) circulates as four antigenically distinct serotypes whose dominance fluctuates over time in many endemic regions, a phenomenon known as serotype shift that is frequently associated with large outbreaks and increased disease severity. This review, through a synthesis of epidemiological, virological, immunological, entomological, and environmental evidence, observes that serotype shift likely arises from the interaction of multiple determinants rather than solely from viral evolution, with population immunity playing a central role. The accumulation of serotype-specific herd immunity, together with short-lived cross-protection and Antibody-Dependent Enhancement (ADE), reshapes population susceptibility and creates ecological space for heterologous serotypes with higher transmission potential. The synthesis of global dengue studies indicates that these immune dynamics interact with viral genetic diversity, vector competence, climate variability, and human factors such as demography, socioeconomic status, population density and mobility to drive cyclical and sometimes abrupt changes in serotype dominance. Notably, the review indicates that serotype changes often precede or coincide with more clinical severity and patterns of outbreaks, with direct implications for the process of forecasting outbreaks, vaccine performance, and preparedness to respond with appropriate health measures. On the whole, this review confirms the opinion that the change of dengue serotype occurrence becomes a consequence of interconnected biological and ecological processes involved in the transmission of dengue serotype shifts in hyperendemic areas.</t>
+          <t>Atopic dermatitis (AD) is the most common inflammatory skin disease in the pediatric age group, affecting 15%-20% of children globally. Initial treatment modes include hydration, occlusive topical medicines, antimicrobial treatment, phototherapy, and systemic immune suppressants in the case of severe to moderate refractory AD. However, there is a lack of head-to-head studies on the choice of topical and systemic therapies for moderate to severe AD in the pediatric age group. This systematic review aimed to determine the efficacy and safety of topical and systemic treatments for moderate-to-severe AD in the pediatric age group. A systematic review was performed following the Preferred Reporting Items for Systemic Reviews and Meta-Analyses (PRISMA) guidelines. A search of articles was done from PubMed and Google Scholar from 1975 to 2023. We found a total of 1114 possible clinical trials. Of these, 68 articles fulfilled the eligibility criteria. Thirty-four articles discussed topical therapies, which included corticosteroids, calcineurin inhibitors, and emollients, and 34 articles were about systemic therapies, consisting of cyclosporine, dupilumab, upadacitinib, thymopentin, omalizumab, antihistamines, probiotics, and others. Out of 68 studies, 41 were randomized controlled trials. Based on the study results, we conclude that topical steroids and calcineurin inhibitors are effective and safe in mild to moderate pediatric AD. It was also demonstrated that while systemic monotherapy with dupilumab (in age groups younger than 6 months) and JAK inhibitors (like abrocitinib and upadacitinib in those younger than 12 years) is highly effective in rapidly reducing severity scores, their high cost and limited availability restrict their use in countries like India. In such settings, cyclosporine (and sometimes oral prednisolone in tapering doses over 2 weeks) is still recommended as a first-line therapy in severe AD while planning for steroid-sparing agents.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42357692/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40097336/</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.5219</v>
+        <v>0.7122000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -726,46 +726,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42286757</t>
+          <t>34899901</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Autochthonous dengue transmission in Europe: epidemiology, mechanisms, and modelling insights.</t>
+          <t>Different Approaches to Atopic Dermatitis by Allergists, Dermatologists, and Pediatricians.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Campinopoli G; Caro AD; D'Alise A; Conventi F; McHugh TD; Melino G; Zumla A; Ippolito G</t>
+          <t>Zuccolo de Bortoli SP; Chong Neto HJ; Rosário Filho NA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Biology direct</t>
+          <t>Dermatology research and practice</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10.1186/s13062-026-00868-3</t>
+          <t>10.1016/j.jaip.2015.08.006</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Dengue is the most rapidly expanding arboviral infection globally, with rising incidence and widening geographic distribution driven by urbanisation, climate change, vector expansion, and global mobility. Although traditionally confined to tropical and subtropical regions, dengue is increasingly emerging in temperate settings, including Europe. Recent outbreaks in Italy, Spain, and France, together with evidence of under-recognised transmission, indicate a transition from sporadic importation to recurrent autochthonous infection. This shift is facilitated by the establishment of Aedes albopictus, increasing climatic suitability, an increase in case importation from endemic areas and delays in clinical recognition and public health response. In non-endemic regions, dengue presents distinct challenges, including low population immunity, limited clinical awareness, and diagnostic constraints that may hinder early detection. While advances in vaccines, particularly TAK-003, and novel vector control strategies such as Wolbachia-based interventions offer new opportunities, their role in Europe remains context-specific and complementary to strengthened surveillance and preparedness systems. Modelling approaches provide valuable decision support but are constrained by data limitations in emerging settings. The emergence of dengue in Europe should be viewed as an early signal of broader changes in vector-borne disease dynamics. Proactive investment in integrated surveillance, diagnostics, vector control, and targeted vaccination strategies will be essential to mitigate future risk and prevent sustained transmission in non-endemic regions.</t>
+          <t>Atopic dermatitis (AD) is the most prevalent chronic inflammatory skin disease, with a vast drug arsenal and guidelines available for its management and diagnosis and different medical specialties engaged in providing care. This study aimed to outline the therapeutic and diagnostic approaches to the AD of allergists, dermatologists, and pediatricians and verify whether they are compliant with the guidelines. A cross-sectional study using an electronic questionnaire administered through the SurveyMonkey® platform was disclosed by participating medical societies to their medical associates. Of the 1,473 participating physicians, the use of moisturizers as part of AD treatment was observed among pediatricians (91.9%), dermatologists (97.5%), and allergists (100%;  There were differences in the therapeutic and diagnostic approaches to AD used by allergists, dermatologists, and pediatricians and those recommended by the guidelines, especially regarding the use of wet-wrap therapy, proactive treatment with topical corticosteroids or calcineurin inhibitors, prescription of anti-histamines, recommendation of phototherapy, and control of aeroallergens.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42286757/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34899901/</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.5159</v>
+        <v>0.6965</v>
       </c>
     </row>
     <row r="8">
@@ -776,46 +776,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>42347609</t>
+          <t>39634513</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bridging the Gaps in Dengue Control in Latin America: Multisectoral Strategies from an Expert Panel.</t>
+          <t>A systematic review of guidelines for the management of atopic dermatitis in children.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tejada CE; Aizenberg M; Cucunubá Z; Rodríguez WC; Bazán JD; Terrón FAG; Gutiérrez G; Cuentas AL; Casapia Morales M; Núñez JGM; Mojica JA; Orduna T; Robles VP; Rico-Restrepo M; Torres JR; Soto MJV; Vélez ID</t>
+          <t>Deva M; Netting MJ; Weidinger J; Brand R; Loh RK; Vale SL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaccines</t>
+          <t>The World Allergy Organization journal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10.1186/s40249-018-0464-x</t>
+          <t>10.1097/DER.0000000000000895</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>In March 2025, the Americas Health Foundation (AHF) convened a regional meeting, in Bogotá, Colombia, of the Latin America Dengue Task Force, a multidisciplinary regional group of arbovirus specialists, to address the growing challenges posed by dengue in the region. The primary objective of the meeting was to analyze the regional dengue landscape, identify gaps and barriers that hinder a comprehensive approach, and develop a strategic blueprint for advancing control and prevention in Latin America. The Task Force conducted a thorough review of dengue-related issues, drawing on participants' professional expertise in vaccination, prevention, diagnosis, treatment, vector control, environmental determinants, and regulatory and policy frameworks. Key barriers identified include underreporting, widespread insecticide resistance, structural weaknesses in the health system, fragmented surveillance, financial and political constraints, and socioeconomic drivers. Based on these findings, actionable recommendations were developed to optimize regional dengue surveillance, strengthen prevention and diagnosis strategies, and improve coordination among stakeholders. This narrative review summarizes the epidemiological context, presents expert guidance to overcome existing limitations, and outlines strategies to advance integrated dengue control in Latin America.</t>
+          <t>Atopic dermatitis (AD) is a chronic disease that is increasing in prevalence, particularly in children and people with skin of colour. Current management involves topical treatments, phototherapy and immunosuppressants, as well as newer therapies like dupilumab. Health professionals should also be aware of the specific management considerations for AD in people with skin of colour. This systematic review was conducted to examine global guidelines for the management of AD in children, compare management recommendations, examine specific recommendations for children with skin of colour, and assess the quality of the guidelines. The databases Medline, Embase, CINAHL, Scopus, Guidelines International Network, and Emcare Nursing and Allied Health were searched to identify guidelines or articles relating to the management of AD in children from 1990 to 2023. A grey literature search was also undertaken. The recommendations from the guidelines were extracted and compared, and the quality of the guidelines was assessed using the Appraisal Guidelines for Research and Evaluation (AGREE) II tool. A total of 1644 articles were identified from the initial search. Title and abstract screening, full text screening, and reference checking yielded 28 guidelines for the final appraisal and data extraction. The main variations in management recommendations were the timing of emollients, bleach baths, bath additives, oral antihistamines, and the age cut-offs for topical calcineurin inhibitors. Many guidelines were not updated to reflect newer therapies like dupilumab and topical phosphodiesterase-4 (PDE4) inhibitors. There were minimal recommendations regarding management of skin of colour. Only 12/28 guidelines met the satisfactory cut-off score for the AGREE II appraisal, largely due to a lack of well-documented methodology. This review showed that the recommendations for AD management in skin of colour were consistently lacking. Despite generally consistent management strategies over the last 5 years, less than half of the guidelines met high-quality criteria, emphasising the importance of using tools like AGREE II in future guideline development.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42347609/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39634513/</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.6893</v>
       </c>
     </row>
     <row r="9">
@@ -826,46 +826,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>42348873</t>
+          <t>27676112</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The Evolution of Dengue Virus in India.</t>
+          <t>Infant Skin Care Products: What Are the Issues?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sankaradoss A</t>
+          <t>Kuller JM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Annual review of virology</t>
+          <t>Advances in neonatal care : official journal of the National Association of Neonatal Nurses</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10.1146/annurev-virology-100424-122700</t>
+          <t>10.1097/ANC.0000000000000341</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The evolution of dengue virus (DENV) is highly modulated by pathogen transmission bottlenecks and immunological pressures. These evolutionary events lead to mutations that cause antigenic changes and the replacement of DENV genotypes, which are directly correlated with epidemic magnitude and severe disease. India bears a disproportionately high dengue burden, accounting for nearly one-third of global cases, making it a persistent public health challenge. The periodic recurrence of outbreaks and cocirculation of all four serotypes pose challenges in disease control efforts. Nearly half of the country's population is seropositive for dengue, with varying seropositivity by age and geographical location. The spatiotemporal dynamics of prevalent serotypes in India are often associated with changes in transmission patterns, leading to cyclic outbreaks approximately every 2-3 years. Although multiple genotypes of serotypes have been recorded worldwide, Indian genotypes are highly diverged, with strong intermixing with neighboring countries. This review explores the mechanisms that drive DENV evolution underlying viral transmission bottlenecks, intrahost genetic diversity, and host immune responses. I also highlight the role of preexisting cross-reactive immunity and concurrent coinfections involving more than one serotype or other genetically similar arboviruses in the evolution of DENV. Finally, I outline the impact of DENV evolution on vaccine development and deployment in India.</t>
+          <t>Infant skin is susceptible to dryness and irritation from external factors, including topical skin care products not formulated for the infant's skin. This may increase the risk of contact dermatitis. Parents frequently express concern regarding potential harm from ingredients in skin care products and seek information. This is complicated by several skin care myths. The purpose of this literature review was to provide evidence-based information to educate parents on the use of products for preterm and term infants. Multiple searches using PubMed were conducted including the search terms "infant skin care," "infant products," "infant bath," "emollients," "diaper skin care," and "diaper wipes." Reference lists of comprehensive reviews were also scanned. Google searches were used to assess consumer information, product information, and regulatory guidelines. There is little scientific evidence to support safety of natural/organic products on infant skin. Raw materials originate from different sources, complicating testing and comparisons of ingredients. Research shows that cleansers formulated for infant skin do not weaken the skin barrier the way harsher soaps and detergents can. Oils with the lowest oleic acid content provide a lower risk of irritant contact dermatitis. Nurses must be informed about natural and organic products, preservatives, and fragrances and know the definition of commonly used marketing terms. Decisions regarding the use of infant products in preterm and term infants should be evidence based. More research is needed to support claims regarding the safety of products used on infant skin.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42348873/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/27676112/</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.5064</v>
+        <v>0.6878</v>
       </c>
     </row>
     <row r="10">
@@ -876,17 +876,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>42330388</t>
+          <t>41689191</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[Can Aedes aegypti, vector of the dengue virus, be controlled in Argentina?].</t>
+          <t>Dermocosmetics in Acne Vulgaris: South African Consensus Recommendations With a Focus on Skin of Color.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Gil JF; Gleiser RM; Falvo ML; Castillo PM; Solís J; Mangudo C; Parussini F; Guerenstein PG; Aparicio JP; Gorla DE</t>
+          <t>Visser WI; Kannenberg SM; Prevost A; Khoza N; Pillay L; Wiid KJ; Heydenrych IR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -896,22 +896,26 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Medicina</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Journal of cosmetic dermatology</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>10.1002/jvc2.436</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Since 2009, Argentina has faced recurrent dengue outbreaks, with a notable incidence increase during the 2023-2024 season. Despite following the guidelines from the Pan American Health Organization for controlling the Aedes aegypti mosquito, the disease remains a significant health problem. This review article analyzes the efficacy of the recommended actions and emphasizes the need for operational research to improve implementation. The Control de Aedes aegypti in Argentina traditional approach focuses on prevention, control and containment actions, including environmental sanitation, monitoring and focal control. However, limitations have been identified, such as the presence of asymptomatic cases contributing to arbovirus transmission, mosquito insecticide resistance, and insufficient community participation in eliminating breeding sites. Alternative control measures that have shown effectiveness in other countries are described, such as the autodissemination of larvicides, the release of mosquitoes infected with Wolbachia, the sterile insect technique, indoor residual spraying, and mass trapping. These innovative strategies need to be systematically evaluated to determine their effectiveness. The persistence of dengue outbreaks indicates that current strategies are insufficient. It is essential to integrate alternative approaches and foster collaboration among health agencies, researchers, and the community to improve dengue control in Argentina and prevent future outbreaks.</t>
+          <t>Acne vulgaris is one of the most common dermatological disorders worldwide, affecting both adolescents and adults. It frequently leads to significant psychosocial and physical sequelae, including acne-induced hyperpigmentation and scarring. Beyond pharmaceutical therapies, dermocosmetics-topical formulations enriched with active ingredients in cosmetically elegant vehicles-have emerged as essential partners in acne management. They optimize clinical outcomes by supporting skin barrier repair, reducing irritation associated with conventional treatments, and targeting key pathogenic pathways in acne. However, no region-specific guidance exists to inform the effective use of dermocosmetics in South African patients, particularly those with skin of color. To develop expert consensus recommendations for the use of dermocosmetics in acne vulgaris management within the South African context. This consensus was developed through structured expert meetings and a targeted literature review of current international and local evidence. The panel synthesized clinical experience and research findings to identify key principles for selecting and integrating dermocosmetics into acne treatment regimens. The consensus highlights the multifaceted role of dermocosmetics in addressing core acne pathogenic factors, supporting epidermal barrier function, mitigating treatment-related adverse effects, and managing acne-induced hyperpigmentation in skin of color. Practical recommendations are provided for their use as adjunctive therapy, monotherapy in mild cases, and maintenance therapy to sustain remission. This South African consensus provides a practical, evidence-informed framework for incorporating dermocosmetics into acne management, with particular attention to the needs of patients with skin of color. Adoption of these recommendations may enhance treatment outcomes, adherence, and patient satisfaction across diverse skin types.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42330388/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41689191/</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.5023</v>
+        <v>0.6843</v>
       </c>
     </row>
     <row r="11">
@@ -922,46 +926,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>42294567</t>
+          <t>27768013</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Beyond the Mosquito: Social Determinants of Health and Global Strategies for Aedes-Borne Disease Control.</t>
+          <t>Prospective multicenter survey on the clinical management of pediatric contact dermatitis.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mostafavi H; Jafarzadeh J; Mohamadi E; Mohamadi F; Moradi G; Moghaddam MS; Yaftian F; Ghanbarnejad A; Mozafari M; Rad EH; Noori ES; Najafi M; Takian A; Bakhtiari A; Olyaeemanesh A</t>
+          <t>Ruggiero G; Carnevale C; Diociaiuti A; Arcangeli F; El Hachem M</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tropical medicine &amp; international health : TM &amp; IH</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>10.1111/tmi.70167</t>
-        </is>
-      </c>
+          <t>Minerva pediatrica</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Aedes-borne diseases, including dengue, chikungunya and Zika, have emerged as a growing global health concern, particularly in tropical and subtropical regions. Their spread is not only driven by biological and environmental factors but also shaped by a wide range of social determinants of health (SDH). This systematic review synthesizes available evidence on SDH that shape the transmission, prevention and control of these diseases, as well as the strategies implemented internationally to address them. We conducted five systematic reviews following PRISMA guidelines, each corresponding to one of the major Aedes-borne diseases (dengue, chikungunya, Zika and other Aedes-related illnesses). Searches were performed in PubMed and Scopus for the period 2000-2024, using both MeSH terms and free-text keywords. Quality appraisal was conducted using appropriate checklists, that is, CASP, STROBE and results were synthesized narratively. Thematic coding was applied to identify patterns across social, economic and environmental determinants, while intervention data were summarized descriptively. The systematic search figured out a large number of potentially relevant records across the five reviews. One hundred sixty-nine studies were included for full analysis including 27 studies on Aedes in general, 54 on dengue, 3 on chikungunya, 14 on Zika and 71 on preventive interventions. The main themes that emerged from the study analysis included: Poverty and Related Indicators, Education and Health Literacy, Community Engagement, Urban Infrastructure and Social Support, Access to Health Services, Demographic Factors, Culture and Beliefs and Migration and Human Mobility. Interventions that engaged communities and combined educational, infrastructural and environmental actions demonstrated the greatest impact and sustainability. Findings of the study suggest that effective and sustainable Aedes-borne disease control depends on tackling structural inequities-particularly poverty and poor urban infrastructure-while promoting health literacy and community engagement. Future research should further investigate underexplored determinants, including cultural and migratory factors, to inform context-specific, multisectoral responses.</t>
+          <t>Contact dermatitis can be defined as an inflammatory process affecting the skin surface and induced by contact with chemical, physical and/or biotic agents in the environment. It causes lesions to skin, mucosae and semi-mucosae by means of allergic and irritant pathogenic mechanisms. Among the main triggers of contact dermatitis in the pediatric age are chemical or physical agents, which cause irritant contact dermatitis (ICD), and sensitizers, which cause a tissue damage through an allergic mechanism (allergic contact dermatitis [ACD]). A prospective, multicenter, observational study was carried out in 204 children affected by contact dermatitis, aged up to 14 years, and enrolled by pediatricians from 7 different Italian provinces. The diagnosis of contact dermatitis was based on the pediatrician's clinical evaluation. The data were collected through a series of simple and multiple choice questions, anonymously filled out by pediatricians. In 90% of cases (184 of 204 patients), there was complete remission of contact dermatitis, with no cases of worsening. No adverse events were observed, either. The effectiveness of the therapy was rated as "very effective" by 84.4% of the parents and 86.8% of the pediatricians. In only 10 patients a new therapy had to be prescribed. Contact dermatitis is a heterogeneous inflammatory skin disease induced by contact with different kinds of environmental agents. Cutaneous manifestations are highly variable and depend on the modality of contact, on the causative agent and on the pathogenesis. This Italian experience of a clinical approach to contact dermatitis stresses the need of daily skin care through different therapeutic strategies, based on the diagnosis, the clinical severity and the parents and children compliance. The first therapeutic measure to be implemented is prevention, through the removal of the causative agent and the use of protective devices. Indeed, preserving the skin's barrier function is an important goal and a priority of treatment algorithms.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42294567/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/27768013/</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.4936</v>
+        <v>0.6828</v>
       </c>
     </row>
     <row r="12">
@@ -972,46 +972,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>42286517</t>
+          <t>40911742</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Clinical manifestations and laboratory findings in patients coinfected with dengue virus and SARS-CoV-2: a systematic review.</t>
+          <t>Dermatological Safety of Cosmetic Products Marketed to Children: Insights on the Sephora Kids Phenomenon.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Adnyanaschah R; Abdulah R; Oktora MP</t>
+          <t>Bolen R; Szymanski T; Nichols J; Pulsipher KJ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BMC infectious diseases</t>
+          <t>Journal of drugs in dermatology : JDD</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10.1186/s12879-026-13752-2</t>
+          <t>10.36849/jdd.8800</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Dengue Hemorrhagic Fever and Coronavirus disease 2019 (COVID-19) are infectious diseases caused by dengue virus (DENV) and severe acute respiratory syndrome coronavirus 2 (SARS-CoV-2). While DENV remains endemic in many tropical regions, SARS-CoV-2 spread globally beginning in 2020. Reports of coinfection have emerged from several countries. This systematic review describes the clinical manifestations and laboratory findings reported in patients coinfected with DENV and SARS-CoV-2. This review followed the PRISMA guidelines and collecting data from PubMed for articles published between 2020 and 2025 that discussed DENV and SARS-CoV-2 coinfection. Eligible study designs included theoretical articles, case reports, case series, and cohort studies. Data were synthesized descriptively due to heterogeneity and the absence of comparator groups. Fifteen studies met the inclusion criteria, identifying 65 patients with SARS-CoV-2 and DENV coinfection. Reported symptoms included fever (69%), vomiting (57%), abdominal pain (55%), rash (54%), and shock (51%). Laboratory findings also showed hematological and physiological alterations including hypotension (57.14%), tachypnea (50%), fever (62.5%), neutropenia (33.33%), neutrophilia (50%), lymphopenia (42.86%), and lymphocytosis (28.57%). These percentages represent descriptive counts across heterogeneous case reports and do not reflect prevalence estimates. Patients with DENV and SARS-CoV-2 coinfection exhibit a range of clinical and laboratory abnormalities, but the available evidence-primarily case reports and case series without comparator groups-does not allow conclusions about disease severity or prognosis relative to monoinfection. The findings should therefore be interpreted as descriptive and hypothesis-generating. Careful diagnostic evaluation and clinical monitoring remain essential in suspected coinfection cases. Not applicable.</t>
+          <t>The "Sephora Kids" trend, where children, especially tweens and teens, are increasingly using makeup and skincare products marketed by beauty retailers, presents notable dermatological challenges. Although these products can facilitate self-expression and teach self-care, their safety and efficacy for young users are largely unverified. This review examines 4 key ingredients commonly found in these products,retinol, exfoliating acids (AHA and BHA), and vitamin C, to assess their implications for pediatric skincare. Current literature and FDA-approved guidelines indicate that these ingredients have not been thoroughly tested in children. Consequently, using these products without medical supervision can pose risks such as skin redness, irritation, heightened sun sensitivity, dermatitis, and other potential adverse effects. This review underscores the importance of cautious use and highlights the need for further research to ensure the safety of these ingredients in young populations. By informing healthcare providers and consumers of these risks, we aim to promote safer skincare practices among children.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42286517/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40911742/</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.4832</v>
+        <v>0.6787</v>
       </c>
     </row>
     <row r="13">
@@ -1022,46 +1022,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>42272890</t>
+          <t>39586822</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Integrating structured point-of-care ultrasound into dengue fever management: A mini review and comprehensive clinical guide.</t>
+          <t>Moisturizer Use in Children With Atopic Dermatitis: Real-Life Practice, Beliefs, and Challenges Among a Cohort of Jordanian Patients.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lee ZY; Chin WV</t>
+          <t>Muhaidat J; Fawwaz AM; Al-Qarqaz F; Alshiyab D; Ashaar-Akhras; Ababneh MM; Ghazou A; Tashtoush S; Abdelnabi T</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>World journal of critical care medicine</t>
+          <t>Pediatric dermatology</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10.5492/wjccm.v15.i2.114264</t>
+          <t>10.1111/pde.15821</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Dengue fever is one of the most common mosquito-borne viral diseases and poses a significant health threat. The primary management involves hydration tailored to the disease stage and severity. Although many cases are mild, dengue can rapidly progress within hours. Complications such as plasma leakage and bleeding are difficult to detect through routine clinical assessment alone. In this context, point-of-care ultrasound (POCUS) has emerged as a valuable bedside tool for the early detection of fluid shifts and plasma leakage. Ultrasound findings in dengue-related plasma leakage include gallbladder wall thickening, ascites, pleural effusions, and other third-space fluid shifts. These sonographic signs often precede the clinical presentation of plasma leakage and can serve as early indicators for impending shock. Regular ultrasound assessment facilitates risk stratification and timely intervention, potentially reducing progression to dengue shock syndrome. Currently, there is no validated POCUS protocol specific to dengue assessment. We propose a standardized, structured ultrasound protocol focusing on key diagnostic parameters, coupled with serial serum hematocrit and lactate measurements for a comprehensive evaluation. This approach facilitates earlier identification of at-risk patients, thereby improving patient management, preventing clinical deterioration, and reducing morbidity and mortality associated with severe dengue.</t>
+          <t>Moisturizers are a crucial baseline therapy for atopic dermatitis (AD). To evaluate the real-life experience of using moisturizers in AD patients and to assess parents' opinions and challenges regarding moisturizer use. This cross-sectional study used a questionnaire completed by the parents of pediatric AD patients. The assessment questionnaire evaluated demographic factors as well as practices, opinions, and challenges regarding the use of moisturizers in AD treatment. Applying moisturizers twice daily, considered sufficient use, was evaluated across demographic levels using bivariate analysis. A total of 425 patients with AD participated in the study. The median age was 4 years, 51% of patients were female, 61% had moderate to severe AD, 34% had a family history of AD, and 41% of cases reported sufficient moisturizer use. Factors associated with increased frequency of application of moisturizers included younger age at diagnosis, higher parents' educational level, and increased family income. The twice-daily application versus less frequent application was associated with fewer monthly flare-ups (33% vs. 17%, p &lt; 0.001). Overall, 54% of patient guardians believed that moisturizers were necessary for treating AD, 69% considered fragrance-free formulas to be better, and 86% thought there to be a need for counseling from their physician on using moisturizers in AD treatment. Factors undermining the application of moisturizers included the time needed for application, cost, and lack of patient cooperation. In real-world practice, parents tend to underutilize moisturizers. To address this issue, treating physicians must provide additional education, and health insurance companies should consider covering moisturizers to ensure their accessibility.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42272890/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39586822/</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.4767</v>
+        <v>0.676</v>
       </c>
     </row>
     <row r="14">
@@ -1072,46 +1072,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>42328715</t>
+          <t>31026679</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Beyond Hemostasis: Platelet Biomarkers and Vascular-Immune Crosstalk in Dengue.</t>
+          <t>Systematic Review and Meta-analysis Comparing Topical Corticosteroids With Vehicle/Moisturizer in Childhood Atopic Dermatitis.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>da Silva-Alencar ABA; Matos AO; de Sousa DF; Dietz JDC; Hottz ED; da Silva-Sales MFM; Sales-Campos H</t>
+          <t>Fishbein AB; Mueller K; Lor J; Smith P; Paller AS; Kaat A</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FASEB journal : official publication of the Federation of American Societies for Experimental Biology</t>
+          <t>Journal of pediatric nursing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10.1096/fj.202600884RR</t>
+          <t>10.1111/j.1365-2133.2012.11177.x</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Dengue is an arboviral disease with major global public health impact. Its pathophysiology involves complex interactions between the virus and the host, including the immune response and the vascular endothelium. In this context, platelets play roles beyond hemostasis, acting as key immunomodulatory cells involved in inflammation and the regulation of vascular permeability. Therefore, this review summarizes and discusses the so called classic and non-classic platelet-related and endothelial biomarkers described in dengue virus infection. Classical biomarkers include P-selectin (CD62P), PF4/CXCL4, RANTES/CCL5, CD40L, IL-1β, VEGF, integrin αIIbβ3, CD63, and platelet extracellular vesicles, all supported by broad experimental and clinical evidence. Non-classical or emerging biomarkers include TLT-1, TREM-1/sTREM-1, angiopoietins (Ang-1/Ang-2), serotonin, ferritin, dengue virus envelope domain III (EIII), and soluble endothelial molecules such as IL-1RA, sCD163, SDC-1, sVCAM-1, IL-8, and IP-10. Alone or in combination, these markers can be used/explored as prognostic tools and/or as therapeutic targets. Finally, integrating multimarker panels encompassing hemostatic, inflammatory, and endothelial pathways may improve prognostic stratification. This approach could support targeted interventions and help reduce complications such as thrombocytopenia, plasma leakage, and dengue shock.</t>
+          <t>To determine the safety and efficacy of topical corticosteroid versus vehicle/moisturizer in children under 2 years old (&lt;2 y). A systematic review and meta-analysis searching PubMed MEDLINE, Embase, Web of Science, Cochrane Database of Controlled Trials, Cochrane Database of Systematic Reviews, DARE, NHS Economic Evaluation, CINAHL, GREAT, and Clinicaltrials.gov. We selected randomized controlled trials (RCTs) comparing topical corticosteroids to vehicle/moisturizer and included children &lt;2 y. Two authors extracted data. Only one study limited analyses to children &lt;2 y, so our review included participants older than 2 years. Twelve RCTs were included with 2224 participants. Ten studies were industry-sponsored. The proportion of responders to topical corticosteroid across studies was 0.65 (95% CI, 0.54-0.74), as compared to vehicle/moisturizer 0.32 (95% confidence interval (CI), 0.20-0.48). The proportion of adverse events were similar between groups (topical steroids 0.17 (95% CI, 0.08-0.33) vs. vehicle/moisturizer 0.12 (CI 0.02-0.42)). High heterogeneity in treatment response occurred across studies that could not be explained by potential moderators. Mild adrenal suppression occurred in 4 of 157 measured participants (3%) receiving topical corticosteroids. Limitations include the few RCTs on this topic, the inclusion of participants &gt;2 y and outcome measures and reporting methods rarely met CONSORT guidelines. Topical corticosteroids trended to being more effective and equally safe to vehicle/moisturizers, but generalizability is limited given the dearth of well-designed studies focused on children &lt;2 y. Adverse events from vehicle/moisturizer may be greater than topical corticosteroid due to under treatment. Further work is needed in this age group.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42328715/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/31026679/</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.458</v>
+        <v>0.676</v>
       </c>
     </row>
     <row r="15">
@@ -1122,46 +1122,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>42347620</t>
+          <t>34623061</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Advances and Challenges in Vaccine Development for West Nile Virus (WNV) Infection.</t>
+          <t>Efficacy of moisturizers in paediatric atopic dermatitis: A systematic review and meta-analysis of randomised controlled trials.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Gupta A; Tripathi A; Jha K; Rawat Y; Bhardwaj U; Khasa R; Chauhan S</t>
+          <t>Kritsanaviparkporn C; Sangaphunchai P; Treesirichod A</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaccines</t>
+          <t>Indian journal of dermatology, venereology and leprology</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10.3390/vaccines12121398</t>
+          <t>10.25259/IJDVL_1384_20</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>West Nile Virus (WNV) belongs to the orthoflavivirus genus and is part of the Flaviviridae family, which includes the Japanese encephalitis virus, Dengue virus, Zika virus, and yellow fever virus. WNV circulates among birds and mosquitoes, posing infection risks to humans and mammals. The significant rise in WNV's geographic spread and infection rates over the past five decades has prompted urgent public health concerns, driving the need for accelerated vaccine research. The development of a vaccine for WNV infection presents several challenges, primarily due to the virus's complex biology, the risk of cross-reactivity with other flaviviruses, safety concerns such as antibody-dependent enhancement (ADE), and the economic and logistical hurdles in vaccine production. Despite significant research efforts, no human vaccine has been approved, although several candidates are in various stages of development. The current review offers a comprehensive summary of the latest progress and the concomitant challenges in the development of vaccines. It also discusses the role of host-pathogen interaction, host immunity, viral immune evasion, and disease pathogenesis in facilitating the advancement of vaccines.</t>
+          <t>Topical moisturizer is recommended for atopic dermatitis. The aim of the study was to investigate the knowledge gap regarding the efficacy of moisturizer in young patients. A systematic review and meta-analysis were conducted on randomised controlled trials comparing participant's ≤15 years with atopic dermatitis, receiving either topical moisturizer or no moisturizer treatment. Certainty of evidence was assessed using the Grading of Recommendations, Assessment, Development and Evaluation (GRADE) framework. Six trials were included (intervention n= 436; control n= 312). Moisturizer use extended time to flare by 13.52 days (95% confidence interval 0.05-26.99, I2 88%). Greater reduction in risk of relapse was observed during the first month of latency (pooled risk ratio 0.47, 95% confidence interval 0.31-0.72, I2 28%) compared to the second and third months (pooled risk ratio 0.65, 95% confidence interval 0.47-0.91, I2 35% and pooled risk ratio 0.63, 95% confidence interval 0.47-0.83, I2 33%, respectively).Treated patients were 2.68 times more likely to experience a three-six months remission (95% confidence interval1.18-6.09, I2 56%). Moisturizer minimally improved disease severity and quality of life. There is a dire need to conduct randomised controlled trials with more robust and standardised designs. Moisturizer benefits young patients with atopic dermatitis. However, more research is needed to better estimate its efficacy.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42347620/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34623061/</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.4473</v>
+        <v>0.6736</v>
       </c>
     </row>
     <row r="16">
@@ -1172,46 +1172,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>42344632</t>
+          <t>40170321</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>The role of platelet transfusion in modulating platelet indices and leukocyte dynamics in dengue fever patients.</t>
+          <t>Safety of Petroleum-Based Emollients in Pediatric Atopic Dermatitis.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Afzal M; Chandrasekar M; Sah AK; Agarwal S</t>
+          <t>Ghali H; Krenitsky A; Albers SE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian journal of transfusion science</t>
+          <t>Clinical pediatrics</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10.4103/ajts.ajts_190_24</t>
+          <t>10.1177/00099228251331443</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Dengue fever, a viral illness transmitted by Aedes mosquitoes, is marked by a reduction in platelet count (PLT) and changes in blood parameters, which increase the risk of complications such as hemorrhage. Platelet transfusion is frequently used to counter thrombocytopenia in dengue cases, but the precise effects on platelet indices (such as mean platelet volume [MPV] and platelet distribution width [PDW]) and leukocyte counts are still not well defined. This literature review investigates the role of platelet transfusions in modifying platelet and leukocyte dynamics in dengue patients. Studies reveal that transfusions can temporarily increase PLTs, offering short-term hemostatic stability. Changes in platelet indices post-transfusion include increased MPV and variable PDW, potentially reflecting reactive changes in the bone marrow and platelet population. Leukocyte counts show inconsistent responses, with some reports indicating a transient rise following transfusion, possibly linked to immune responses to transfused platelets. While platelet transfusion offers symptomatic relief, these findings highlight the complex interactions within the hematological system following transfusion and underscore the need for caution in transfusion practices. Further investigation is essential to delineate optimal transfusion thresholds, better predict hematological responses, and minimize potential risks associated with transfusions in dengue patients.</t>
+          <t>Atopic dermatitis (AD) is a chronic inflammatory skin condition that severely impacts the quality of life of both children and adults. Effectively managing AD entails addressing acute inflammatory symptoms, avoiding triggers, and preserving the homeostasis of the skin barrier with emollients. Petrolatum-based emollients are affordable occlusive agents that prevent moisture loss and create a protective layer on the skin to support healing; however, apprehensions, often stemming from safety-related information circulating on social media and mobile applications, have led to increased reluctance among parents and caregivers to use these products to treat their child's AD. This review aims to consolidate the available information in the literature concerning the safety of petrolatum-based emollients while comparing this with the information found in popular mobile applications used to check product safety and health information.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42344632/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40170321/</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.4275</v>
+        <v>0.6699000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1222,46 +1222,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>42256613</t>
+          <t>32524381</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nanoparticle vaccine formulations for dengue virus.</t>
+          <t>Efficacy of Nonprescription Moisturizers for Atopic Dermatitis: An Updated Review of Clinical Evidence.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Murphy CT; Ainslie KM</t>
+          <t>Hebert AA; Rippke F; Weber TM; Nicol NH</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RSC pharmaceutics</t>
+          <t>American journal of clinical dermatology</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10.1016/j.jconrel.2019.11.022</t>
+          <t>10.3390/children6020017</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Dengue virus (DENV) is one of the most prevalent mosquito-borne pathogens, with almost half of the global population at risk of infection. While most cases are mild, severe illness and even death is not uncommon. There are currently a lack of available antivirals and highly effective prophylactic vaccines available for DENV, leading to a significant gap in protection. While live-attenuated vaccines have been developed and briefly utilized, some have been found to increase the risk for developing antibody-dependent enhancement (ADE), a phenomenon that can worsen outcomes in those who are exposed to DENV after receiving the vaccination. Nanoparticle-based vaccine formulations provide numerous advantages over live-attenuated vaccines such as controlled release, dose-sparing, and ability to effectively encapsulate adjuvants and viral antigens, while simultaneously minimizing the risk for development of ADE. Numerous carrier systems have been developed, including polymeric, lipid, inorganic, and protein-based formulations. Each system has been found to induce unique antigen-specific immune activation that includes varying degrees of humoral and cellular immune responses. While there is still much research to be done, nanoparticle-based vaccine formulations offer a promising approach to combat the growing threat of DENV.</t>
+          <t>Twice-daily moisturization is recommended by international guidelines as the bedrock of the management of atopic dermatitis (AD). Moisturizers should be selected based on proven clinical effectiveness in improving the skin barrier and improving the symptoms of AD. We searched the PubMed database for clinical trials assessing daily moisturization for the treatment of AD published between 2006 and 2019. Studies had to assess the efficacy of commercially available moisturizers using objective measures of corneometry, transepidermal water loss, or incidence of flare as endpoints, and treatments had to be currently available to patients. Clinical studies showed that moisturization (typically twice daily) significantly improved the skin barrier in adults and children with AD. Longer-term flare studies showed that daily moisturization reduced the incidence of flares and extended the time between flares. Proactive moisturization of infants at high risk of developing AD may reduce its manifestation. Therapeutic moisturizers for AD are specifically formulated with ingredients that target symptoms of AD, such as itch, inflammation, or compromised skin barrier. The US FDA requires that any moisturizer available in the USA and claiming to treat AD must contain colloidal oatmeal. Healthcare providers can maximize compliance and outcomes by educating patients on the benefits of liberally applying a therapeutic moisturizer twice daily to support the skin barrier and help reduce the incidence of flares. Specific recommendations should be for clinically tested moisturizers evaluated using objective, validated skin assessments.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42256613/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/32524381/</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.422</v>
+        <v>0.6688</v>
       </c>
     </row>
     <row r="18">
@@ -1272,46 +1272,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>42303089</t>
+          <t>37779485</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Global performance of predictive models for dengue severity, hospitalization and mortality: a systematic review and meta-analysis of 146 studies.</t>
+          <t>A practical approach to caring for atopic dermatitis in children.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Delpino FM; Peres IT; Gusberti T; de Lima CJ; Duque S; Merson L; Garcia-Gallo E; Hamacher S; Ranzani OT; Bozza FA; Bastos LSL</t>
+          <t>Bayer DK</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>International journal of infectious diseases : IJID : official publication of the International Society for Infectious Diseases</t>
+          <t>Current opinion in pediatrics</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10.1016/j.ijid.2026.108879</t>
+          <t>10.1097/MOP.0000000000001293</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Predictive models are increasingly used to support the clinical management of dengue, but their performance varies widely across settings. We aimed to evaluate multivariable prediction models for dengue severity, mortality, and hospitalization, and to summarize the predictors most consistently associated with these outcomes. We searched five databases for studies that developed or validated multivariable models predicting severity, hospitalization, or mortality in dengue populations. Two reviewers independently selected studies and extracted data, and risk of bias was assessed with PROBAST. We pooled diagnostic accuracy estimates using bivariate models and synthesized predictor effects with random-effects meta-analyses. A total of 146 studies were included: 109 addressed severity, 42 mortality, and 12 hospitalizations. For severity, pooled sensitivity was 0·85 (95% CI 0·82-0·87) and the overall AUC was 0·93 (0·91-0·94), with machine learning models slightly outperforming traditional regression (AUC 0·93 vs 0·90). PROBAST classified 112 of 146 studies as high risk of bias. Bleeding, shock, and hypoalbuminemia were the predictors most consistently associated with adverse outcomes. Dengue prediction models, especially those based on machine learning, show good discrimination for severity, but the evidence is limited by high risk of bias and scarce external validation.</t>
+          <t>Atopic dermatitis is a chronic, systemic disease with primary cutaneous clinical manifestations and is commonly attributed to an exaggerated Th2 inflammatory response. Recent research regarding risk factors, prevention, clinical features, and management of atopic dermatitis will be reviewed. In the last decade, advances have been made in identifying the factors that either confer increased risk for or protection from atopic dermatitis and associated atopy. Progress has also been made in the clinical management of this disease. Promising biomarkers and therapeutically informative characteristics of this disease have been identified in young children with and without the presence of eczema, but much has yet to be elucidated. Progress has also been made in clarifying the advantages and disadvantages of respective medical managements, including but not limited to topical corticosteroids, topical calcineurin inhibitors, phototherapy, systemic immunosuppressants, and targeted immunotherapy. Given that medical management may show variable efficacy in a child, an optimized skin care regimen is of utmost importance as well. Atopic dermatitis is a challenging, chronic systemic disease that incurs significant morbidity in affected children. Although management options have been somewhat disappointing in years past, promising results have been observed in recent advances in targeted immunotherapy.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42303089/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37779485/</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.4214</v>
+        <v>0.6665</v>
       </c>
     </row>
     <row r="19">
@@ -1322,46 +1322,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>42275853</t>
+          <t>38204304</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Global determinants of dengue vaccine acceptance: An updated systematic review and meta-analysis.</t>
+          <t>Systemic treatments in atopic dermatitis in children.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Arriaga-Izabal D; Morales-Lazcano F; Angulo-Zamudio UA; Canizalez-Román A; León-Sicairos N</t>
+          <t>Gürel Dİ; Soyer Ö; Şahiner ÜM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Public health</t>
+          <t>The Turkish journal of pediatrics</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.1016/j.puhe.2026.106350</t>
+          <t>10.24953/turkjped.2023.203</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>To systematically review and quantify the key determinants influencing dengue vaccine acceptance in populations where the vaccine is recommended or considered. Systematic review and meta-analysis. Comprehensive searches were performed in PubMed, Web of Science, Global Index Medicus, and Google Scholar, without date restrictions through April 2026. Eligible studies reported quantitative effect estimates of factors associated with dengue vaccine acceptance. Random-effects inverse-variance models with Hartung-Knapp adjustment, and heterogeneity with I A total of 775 records were identified, with 18 studies meeting inclusion criteria (15 included in quantitative synthesis). In pediatrics, a positive attitude toward vaccination was linked with higher acceptance (OR: 5.66, 95% CI: 2.74-11.7; I Dengue vaccine acceptance may be influenced more by attitudes and prior experiences than by demographic factors alone; however, substantial heterogeneity, reliance on cross-sectional evidence, and very low certainty ratings limit confidence in these findings. Public health strategies should prioritize strengthening vaccine confidence, enhancing risk perception among dengue-naïve populations, and leveraging prior vaccination behaviors, while addressing structural barriers to ensure equitable access.</t>
+          <t>Atopic dermatitis (AD) is a very common skin disease caused by inflammatory reactions, in which the main symptoms of severe itching and recurrent eczema diminish quality of life. As epidermal barrier function and the immune system play a critical role in atopic dermatitis, promoting IgE-mediated sensitization can be the main targets of AD treatment. The goal of AD treatment should be to eliminate the symptoms and obtain longterm eczema control with a multi-step approach adapted to the severity of the disease. Basic management for all patients comprises the use of moisturisers and avoiding triggers. While topical therapy is effective for most children diagnosed with AD, there may also be children who require systemic therapy. The aim of this paper was to present an extensive review of the systemic agents commonly used in childhood atopic dermatitis which mainly target cutaneous inflammation.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42275853/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/38204304/</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.4082</v>
+        <v>0.6647</v>
       </c>
     </row>
     <row r="20">
@@ -1372,46 +1372,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>42292375</t>
+          <t>32867653</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Proteomic signals are not equal clinical phenotypes: redefining evidence standards in arbovirus-SARS-CoV-2 cross-reactivity.</t>
+          <t>Brief Academic Review and Clinical Practice Guidelines for Pediatric Atopic Dermatitis.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Salvador Ibarra IJ; Mora Guzmán Z; Borrás Enríquez AJ; Alpuche J; Castañeda-Hernández G; Pérez-Campos E; Hernández-Huerta MT; Cabrera-Fuentes HA</t>
+          <t>Yang YB; Gohari A; Lam J</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Frontiers in immunology</t>
+          <t>Current pediatric reviews</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>10.1016/j.isci.2025.114375</t>
+          <t>10.2174/1573396316999200820163434</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>The interaction between SARS-CoV-2 and dengue virus represents a biologically plausible yet clinically unresolved challenge in regions where both pathogens co-circulate. Emerging omics-based studies propose that prior SARS-CoV-2 exposure may shape a distinct dengue phenotype through immune imprinting and antibody-dependent mechanisms. However, whether these molecular signals translate into clinically meaningful outcomes remains unclear. This Perspective argues that current evidence remains preliminary and insufficient for clinically actionable interpretation, particularly regarding the conflation of group-level proteomic signals with patient-level clinical phenotypes. Using a recent pilot proteomic study as an illustrative example, we highlight key methodological constraints, including pooled sampling, limited sample size, inadequate control of confounding, and absence of longitudinal and clinical validation. We propose a framework for advancing from exploratory omics observations to clinically interpretable evidence, emphasizing patient-level resolution, temporal dynamics, statistical rigor, functional validation, and integration with standardized clinical endpoints. We also examine the clinical and public health consequences of premature inference, including the potential for premature clinical interpretation, overestimation of disease associations, and challenges in translational interpretation. We conclude that proteomic signals should be regarded as hypothesis-generating rather than predictive until supported by robust, reproducible, and clinically anchored evidence.</t>
+          <t>In this clinical guidelines article, we first include a brief review of the epidemiology, pathogenesis, clinical diagnoses, and scoring-scales for pediatric atopic dermatitis (AD). We then offer a set of pharmacologic treatment guidelines for infants and toddlers (&lt;2 years), children (2-12 years), and adolescents (&gt;12 years). We recommend irritant avoidance and liberal emollient usage as the cornerstone of treatment in all age-groups. In infants &lt;2 years, we recommend topical corticosteroids as first-line medication-based therapy. In infants as young as 3 months, pimecrolimus, a topical calcineurin inhibitor, may also be used. As a last resort in patients &lt;2 years, non-traditional therapies, such as the Aron regime, may be a safer option for refractory or resistant AD before off- label medications are considered. In children and adolescents &gt;2 years, topical corticosteroids are still considered first-line therapies, but there is sufficient safety data to utilize topical calcineurin inhibitors and topical PDE4 inhibitors as well. In children ages 2-12 years whose atopic dermatitis fails to respond to prior treatments, oral systemic immunosuppressants can be used. For adolescents &gt;12, the biologic, dupilumab, is an additional therapeutic option. A trial of phototherapy may also be utilized in children, particularly in adolescents &gt;12 years, if they have access to treatment. Although not currently approved for the treatment of AD, Janus-kinase (JAK) inhibitors represent a promising new class of biologics with recently completed phase III clinical trials (JADE-- MONO1/2).</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42292375/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/32867653/</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.3931</v>
+        <v>0.6633</v>
       </c>
     </row>
     <row r="21">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>42294909</t>
+          <t>42046609</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Role of quaternary epitopes in eliciting broad neutralization response against multiple flaviviruses.</t>
+          <t>Holistic Skincare Approach of Cleanse-Treat-Moisturize-Protect (CTMP®) in Atopic Dermatitis Management: Indian Perspectives, Evidence, and Future Directions.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Chatterjee A; Mangala Prasad V</t>
+          <t>Choudhary S; Sadana D; C V; Sen D; Iyer S</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1442,26 +1442,2710 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Journal of virology</t>
+          <t>Cureus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10.1128/jvi.01777-25</t>
+          <t>10.7759/cureus.105971</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Flaviviruses, or orthoflaviviruses, are arthropod-borne RNA viruses that pose a significant global health threat and co-circulate in many regions across the world. Neutralizing antibodies against specific pathogenic flaviviruses, such as dengue virus, Zika virus, and West Nile virus, are well-known. However, vaccine and therapeutic development against many flaviviruses remains challenging due to their antigenic diversity and complex humoral responses. Recent studies have reported patient-derived neutralizing antibodies that are active against multiple flaviviruses. Structural characterization of these pan-flavivirus antibodies has identified quaternary epitopes that are conserved across multiple flaviviruses, emphasizing the importance of quaternary epitopes on native flaviviruses, which, in some cases, are also preserved across different virus morphologies. Understanding the basis of quaternary structural epitope recognition can aid in the design of immunogens that elicit broad protection, with a lower risk of infection enhancement. In this review, we discuss mechanistic insights of bnAbs targeting different quaternary epitopes found on pathogenic flaviviruses, and implications for next-generation pan-flavivirus vaccine strategies.</t>
+          <t>Atopic dermatitis (AD) is a chronic, relapsing inflammatory dermatosis characterized by epidermal barrier dysfunction, immune dysregulation, and significant impairment in quality of life, particularly among pediatric populations. Although topical anti-inflammatory therapies remain central to acute flare control, growing evidence supports barrier-directed skincare as a fundamental component of long-term disease management. This narrative review synthesizes current evidence on cleansing, moisturization, photoprotection, and preventive strategies in AD, with specific consideration of pediatric care and real-world challenges within the Indian healthcare context. Clinical studies consistently demonstrate that regular emollient use enhances skin hydration, accelerates barrier recovery, alleviates symptom burden, and improves quality of life, with additive benefits when combined with topical corticosteroids. National guidance further emphasizes age-appropriate bathing practices, including delayed bathing in low-birth-weight infants and gentle cleansing followed by prompt emollient application. Despite these recommendations, Indian surveys reveal persistent gaps in caregiver awareness, delayed diagnosis, intermittent moisturizer use, and suboptimal adherence driven by cost constraints, loss to follow-up, and preference for alternative therapies. While emerging modalities, including biomimetic formulations, digital health platforms, and personalized skincare, offer potential future directions, current evidence remains largely exploratory, with limited data on cost-effectiveness and real-world implementation. Overall, barrier-focused skincare represents an important adjunct to pharmacologic therapy in AD; however, effective integration into Indian clinical practice will require strengthened caregiver education, context-specific guidance, and system-level strategies addressing accessibility and adherence, supported by future pragmatic trials and epidemiological studies to enable scalable, evidence-based care.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42294909/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42046609/</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.3758</v>
+        <v>0.6611</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>40267862</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Global perspective on the incidence, severity, and management of diaper dermatitis in neonates, infants, and young children.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Jaiyeoba O; Visscher MO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Journal of tissue viability</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>10.1016/j.jtv.2025.100905</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>We aimed to determine the incidence and severity of diaper dermatitis (DD) among neonates, infants and young children and identify the most effective treatment strategies with a global perspective. We conducted a narrative review of literatures searches from PubMed, EMBASE, and SCOPUS, found 1996 citations, selected primary source papers on infants and children ≤36 months and critically reviewed reports on incidence, severity, and treatment. The analysis produced information on DD incidence and diaper skin care habits from 7500 subjects in 12 countries including extremely premature infants. Three studies suggested that dark-skinned infants had lower incidence and/or severity versus light-skinned subjects. Treatments were generally effective but varied somewhat in rate and/or extent of DD reduction. Variations in DD assessment methods, study design, and starting severity were limitations for comprehensive treatment comparison. DD incidence is relatively high, ranging from 36 to 75 % in home and hospital settings, with severe cases from 1 to 24 %. The review suggests that treatments with "drying" processes or ingredients are promising strategies for improved outcomes. It highlights skin care practices that may reduce DD and prompts questions for future research to understand and manage conditions for optimum skin function in the diaper environment.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40267862/</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.6585</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>30266868</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Recent Developments in Atopic Dermatitis.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Yang EJ; Sekhon S; Sanchez IM; Beck KM; Bhutani T</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pediatrics</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>10.1542/peds.2018-1102</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis (AD) is a bothersome and common skin disease affecting ∼10.7% of children in the United States. This skin condition significantly decreases quality of life in not only patients, but in their families as well. Pediatricians are often the first physicians to diagnose and manage these patients and thus are relied on by families to answer questions about this disease. AD is complex, multifactorial, and has historically had limited therapeutic options, but the landscape of this disease is now rapidly changing. Pathways contributing to the pathogenesis of this disease are continually being discovered, and new therapies for AD are being developed at an unprecedented rate. With this article, we will review the current guidelines regarding the management of AD, outline updates in the current understanding of its pathophysiology, and highlight novel developments available for the treatment of this burdensome disease.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/30266868/</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.6582</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>40912674</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Analysis of the main characteristics of children's skin moisturizers in the Brazilian market.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Branchi BRR; Kiszewski AE; Bonamigo RR</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Jornal de pediatria</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>10.1089/derm.2024.29031.abstracts</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>One of the possible causes of skin microbiome imbalance is the use of dermocosmetics with inadequate pH. This study aims to critically evaluate several children's moisturizers regarding their characteristics so that we can verify the tendency of the products available on the market and whether they are slightly acidic. The importance of dermocosmetics formulated without ingredients with allergenic potential is also discussed in this work. Observational, analytical, cross-sectional and quantitative study. Several brands of children's moisturizers were selected and divided into two groups: group 1 (G1), with moisturizers focused on the care of children with normal skin; and group 2 (G2), with moisturizers with a therapeutic focus on atopic children. We analyzed the pH of each one of the moisturizers, as well as cost, presence of potentially allergenic components and other data contained in the packaging. The members of G1 had an average pH of 5.81 ± 0.35, while the members of G2 had an average pH of 5.42 ± 0.28, with this difference being considered statistically significant (p ≤ 0.001). G1 differed in terms of cost, which was more affordable for the user, when compared to G2 (p ≤ 0.001), but with a predominance of potential allergens in its composition (p = 0.018). This study demonstrates that all moisturizers analyzed in this study respected the acidic pH; however, the group of moisturizers with a therapeutic focus on atopic children had an even lower pH and lower allergenic potential in their composition compared to the group of moisturizers focused on care of children with normal skin.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40912674/</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.658</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>41731580</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>The use of detergents, moisturizers and the experience with therapeutic education among Italian pediatric patients with atopic dermatitis.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Giovannini M; Pertile R; Pucci A; Simonetti G; Geat D; Novembre E; Pace M; Ricci G; Barni S; Mori F; Tomei L; Filippeschi C; Oranges T; Pedaci F; Tronconi G; Peroni D; Galli E; Neri I; Giannetti A; Baldo E</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Italian journal of pediatrics</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>10.1111/j.1525-1470.2008.00813.x</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>BACKGROUND: Daily skin care using appropriate detergents and moisturizers is essential in the management of pediatric atopic dermatitis (AD). Despite guideline recommendations, real-life adherence and caregiver practices vary widely. Therapeutic education is considered a key tool to improve awareness and optimize disease management. The aim of this study is to evaluate the use of detergents, moisturizers, and the experience with therapeutic education among a large cohort of Italian children with AD. METHODS: An observational multicenter study was conducted on 529 pediatric patients aged ≤ 18 year with a physician-confirmed diagnosis of AD, who were evaluated between June 2020 and December 2021 across seven specialized centers in Italy. Clinical and demographic data was collected through physician interviews. Patients’ skin care routines, including cleansing practices and moisturizer use, were analyzed alongside reported therapeutic education experiences. Categorical variables were analyzed using the chi-squared test or Fisher’s exact test; continuous variables were compared using Student’s t-test or the Wilcoxon-Mann-Whitney test, depending on distribution. Normality was assessed with the Kolmogorov-Smirnov test. Statistical significance was set at p-value ≤ 0.05. RESULTS: Overall, 73.9% of patients used lukewarm water for bathing and 74.4% dried their skin by tamponing. Specific detergents were used by 56.0% of participants, most commonly during both flare-ups and remission. A moderate correlation was found between detergent use (ml/week) and body surface area (BSA) (r = 0.300, p-value &lt; 0.0001). Specific moisturizers were used by 65.4% of patients; 73.0% applied them in both acute and remission phases, mainly after bathing. No significant correlation was found between moisturizer volume and BSA (r = 0.087, p-value = 0.085). Therapeutic education was received by 69.0% of families, mainly through physician counseling. Educational exposure was significantly associated with better adherence to recommended practices, including higher usage of specific detergents and moisturizers, more appropriate bathing techniques, and broader product application. Families who received physician-led education also reported significantly greater confidence (p-value &lt; 0.0001) and satisfaction (p-value = 0.007) in managing AD care. CONCLUSIONS: This study highlights significant variability in general washing and moisturizing practices among Italian pediatric AD patients and underlines the potential key role of therapeutic education in improving adherence to skin care, along with greater caregiver confidence and satisfaction. These findings support the implementation of structured, multidisciplinary educational programs to enhance disease management and patient outcomes.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41731580/</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.6578000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>37789992</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Assessment and Management of Atopic Dermatitis in Primary Care Settings: A Systematic Review.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Alqahtani SM; Awaji BH; Mahdi AM; Althawab FH; Aljohani HM; Rayes RA; Shafie RK; Aljohani RA; Alkhorayef S; Alghamdi MK</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>10.7759/cureus.44560</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis is a complex, recurrent, chronic inflammatory skin condition. It frequently begins to manifest in early childhood and may last throughout adulthood. The need for clinical practice guidelines that are based on evidence is critical for efficient and secure care. Little is known about how primary care providers (PCPs) should handle pediatric and adult atopic dermatitis cases and whether they should follow national recommendations. Our systemic review aimed to examine management strategies for treating adult and pediatric (family) atopic dermatitis, including topical calcineurin inhibitors (TCIs), topical corticosteroids (TCS), skin emollients, oral antihistamines, and diet. Data sources were PubMed (MEDLINE) and Embase. Our review investigated English-language articles from 2014 to 2023 that studied the management of adult and children atopic dermatitis. Overall, there were 15 articles included. Surveys and analyses of national databases were the most widely used methods (n=7). The use of TCS by PCPs was common, but they also overprescribed nonsedating antihistamines, favored low-potency drugs, and avoided TCIs. Most studies relied on healthcare personnel reporting their typical behaviors rather than looking at specific patient encounters and it is considered a limitation. Finally, there are gaps in knowledge and management of critical topics such as prescribing TCIs and understanding the safety profiles of TCS, when it comes to treating adult and pediatric atopic dermatitis. Future research in this area is urgently needed because the current systemic assessment is mostly restricted to small studies that assess prescribing behaviors with scant information describing nonmedication management.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37789992/</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.6578000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>29868331</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Atopic Dermatitis: Early Treatment in Children.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Huang A; Cho C; Leung DYM; Brar K</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Current treatment options in allergy</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>10.1007/s40521-017-0140-6</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Therapeutic regimens for the treatment and long-term management of AD traditionally had a two-fold objective of decreasing skin inflammation and repairing the defective skin barrier. Essential treatments for AD in children should include topical moisturizers for skin hydration and prevention of flares, topical anti-inflammatory medications (e.g. corticosteroids, calcineurin inhibitors, PDE4 inhibitor), allergen/irritant avoidance, and treatment of skin infections. Treatment regimens should be severity-based, and implemented in a stepwise approach tailored to the individual patient. This stepwise approach includes initial use of emollients, gentle skin care, and escalating to more potent anti-inflammatory treatments as the disease severity increases. Currently available systemic medications should be reserved for the presence of recalcitrance to topical therapies due to associated toxicities. We believe that early treatment of AD is not only essential in treating the skin disease, but also in preventing the development of additional atopic diseases, such as food allergy, asthma and allergic rhinitis. The defective skin barrier of AD permits a route of entry for food and environmental allergens, and upon exposure, keratinocytes secrete TSLP, which activates the T</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/29868331/</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.655</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>38488957</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Topical steroids or emollients: does order matter?</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ahuja K; Lio PA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Archives of dermatological research</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>10.4103/0019-5154.193677</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Topical corticosteroids, topical steroid-sparing agents, and emollients are all used to treat atopic dermatitis. However, there are no formal guidelines dictating the order and timing in which these topical modalities should be applied. Additionally, the order of application may change drug absorption, efficacy, and distribution. This is especially important for patients with atopic dermatitis. These patients have a dysfunctional skin barrier, which can lead to greater systemic absorption of drugs. Moreover, children already have an increased rate of systemic absorption due to a higher ratio of body surface area to body weight. Thus, the order of application of topical regimens is of the utmost importance in pediatric dermatology. This manuscript presents an updated review of the literature with a focus on guiding clinicians toward the best practices from the available resources.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/38488957/</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.6543</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>35038127</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Topical Ectoine Application in Children and Adults to Treat Inflammatory Diseases Associated with an Impaired Skin Barrier: A Systematic Review.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Kauth M; Trusova OV</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dermatology and therapy</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>10.1007/s13555-021-00676-9</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Inflammatory skin diseases are a significant burden on affected patients. Inflammation is caused by various stress factors to the epidermis resulting in, e.g., dryness, redness, and pruritus. Emollients are used in basic therapy to restore the natural skin barrier and relieve symptoms. A systematic review was performed to evaluate the efficacy and safety of ectoine-containing topical formulations in inflammatory skin diseases characterized by an impaired skin barrier. A systematic review was carried out in PubMed, the Cochrane Library, and Microsoft Academic up to October 2021. Inclusion criteria were ectoine-containing topical formulations (creams, emollients) used for (adjuvant) therapy of inflammatory skin diseases. Clinical studies of any design published in any language were included. A total of 230 references were screened for eligibility, of which six were selected for inclusion in the review (five studies on atopic dermatitis and one study on prevention and management of retinoid dermatitis). The application of topical formulations containing 5.5-7.0% ectoine positively influenced skin dryness and, consequently, pruritus and dermatitis-specific scores in patients with atopic dermatitis. Especially in infants and children, who belong to the most frequently affected group, the formulations were well-tolerated when applied for up to 4 weeks. In studies where ectoine was used as an adjuvant therapy, application was associated with a decreased need for pharmacological therapy and also improved the effectiveness of, e.g., topical corticosteroids. In patients undergoing isotretinoin therapy, ectoine was as effective as dexpanthenol in reducing retinoid dermatitis or improving symptoms. Ectoine is an effective natural substance with an excellent tolerability and safety profile, representing a beneficial alternative as basic therapy or to increase the efficacy of the pharmacological treatment regimen for patients with inflammatory skin diseases, including infants and children.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35038127/</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.6541</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>33863347</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Assessing patients' characteristics and treatment patterns among children with atopic dermatitis.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Geat D; Giovannini M; Barlocco G; Pertile R; Pace M; Mori F; Novembre E; Girolomoni G; Cristofolini M; Baldo E</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Italian journal of pediatrics</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>10.1007/s11739-018-1891-1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis (AD) is the most common immune-mediated skin disease in childhood. Several treatment options for pediatric AD, both topical and systemic, are currently available. We carried out a single-center observational study with the aim of describing characteristics and treatment patterns in pediatric AD patients. The study included 867 patients aged ≤16 years (females 50.5%, mean patient's age 5.9 years, standard deviation ±3.6 years) with a previous doctor-confirmed diagnosis of AD who underwent balneotherapy at the Comano Thermal Spring Water Center (Comano, Trentino, Italy) from April to October 2014. Among the patients included in the study, 41.2% had mild (SCORing Atopic Dermatitis, SCORAD 0-15), 43.6% moderate (SCORAD 16-40) and 15.2% severe AD (SCORAD &gt; 40). A higher occurrence of reported food allergy was observed among children with more severe AD (p &lt; 0.0001), while no association was found between AD severity and reported inhalant allergy or passive smoking (p = 0.15 and 0.92, respectively). Emollients (55.1%) and topical corticosteroids (TCS; 45.7%) were the main treatment options used in the previous month. The use of oral steroids and topical calcineurin inhibitors (TCI) was considerably less common (6.3 and 4.5%, respectively), while no patients were on systemic agents other than steroids. Among patients with severe AD, 9.8% had not used TCS, TCI or any systemic treatments. Moreover, 20.0% of the patients in the study population had followed elimination diets, although only 27.2% of them had a reported food allergy. A significant difference in the prevalence of reported food allergy emerged across the different AD severity categories. Furthermore, although further data are necessary to confirm our findings, undertreatment in children with AD appeared to be very common, at least among those attending the Comano Thermal Spring Water Center. Moreover, many patients followed elimination diets in the absence of reported food allergy.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/33863347/</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.6531</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>33251600</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Unmet medical needs in the treatment of atopic dermatitis in infants: An Expert consensus on safety and efficacy of pimecrolimus.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Luger T; Augustin M; Lambert J; Paul C; Pincelli C; Torrelo A; Vestergaard C; Wahn U; Werfel T</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Pediatric allergy and immunology : official publication of the European Society of Pediatric Allergy and Immunology</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>10.1111/pai.13422</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis (AD) is a common skin disease during infancy, which imposes a considerable burden on patients, their families, and the society, requiring effective treatment options that result in rapid and sustained symptom relief. Additionally, early treatment may prevent the development of atopic comorbidities by restoring the skin barrier. Currently, topical standard-of-care for AD in infants includes emollients and topical corticosteroids (TCS) to treat and reduce the risk of flares. However, only few have been approved for infants and long-term maintenance therapy with TCS is not indicated due to potential local and systemic side effects, including skin atrophy. Accordingly, the recently updated European guidelines for treatment of AD recommend topical calcineurin inhibitors (TCIs) for long-term use, treatment of sensitive skin areas, and for use in the pediatric population. Evidence on the use of TCIs for infants has almost been exclusively collected for pimecrolimus, with &gt;4000 infants evaluated in clinical trials, consistently confirming that pimecrolimus is a safe and effective treatment for infants with AD. Nevertheless, its use is still restricted in most countries to children above the age of 2 years due to initial and mostly theoretical safety concerns. Based on a careful review of the available evidence of clinical trials, post-marketing surveillance, and epidemiological studies, an Expert Panel of European dermatologists and pediatric allergologists concluded that these safety concerns are no longer valid. Therefore, pimecrolimus offers a safe and effective alternative to TCS in infants aged 3 months and above, and labeling restrictions in this age group are no longer justified.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/33251600/</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.6519</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>29858763</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>A Systematic Scoping Literature Review of Publications Supporting Treatment Guidelines for Pediatric Atopic Dermatitis in Contrast to Clinical Practice Patterns.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Siegfried EC; Jaworski JC; Mina-Osorio P</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dermatology and therapy</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>10.1007/s13555-018-0243-4</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Treatment guidelines endorse a variety of strategies for atopic dermatitis (AD) which may vary from published data and clinical practice patterns. The objective of this review was to quantify the volume of available medical literature supporting pediatric AD treatments and compare these patterns to those recommended by published guidelines and/or clinical practice patterns. Searches of Embase (2005-2016) and abstracts from selected meetings (2014-2016) related to AD treatment in patients younger than 17 years of age yielded references that were assessed by study design, primary treatment, age groups, and AD severity. Published literature partially supports clinical guidelines, with emollients and topical medications being the most investigated. There were disproportionately more publications for topical calcineurin inhibitors (TCI) compared with topical corticosteroids (TCS); however, the search interval may have biased the results toward treatments approved near the beginning of the time frame. In contrast, publications documenting clinical practice patterns reflect greater use of emollients and TCS (over TCI), as well as systemic corticosteroids. Data is relatively limited for long-term and combination treatment, treatment of severe AD, and patients younger than 2 years of age, and completely lacking for systemic corticosteroids. This scoping review demonstrates that available medical literature largely supports published guidelines for topical therapy; however, clinical practice patterns are less aligned. There is a lack of data for older, more frequently used generic treatments, including oral antihistamines, oral antibiotics, and systemic corticosteroids. Overall, literature is lacking for long-term treatment, treatment for patients younger than 2 years of age, and for systemic treatment for severe disease. Regeneron Pharmaceuticals Inc.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/29858763/</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.6504</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>30475283</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Diagnosis and Management of Atopic Dermatitis: A Review.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Maliyar K; Sibbald C; Pope E; Gary Sibbald R</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Advances in skin &amp; wound care</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>10.1097/01.ASW.0000547414.38888.8d</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>The purpose of this learning activity is to provide information about the diagnosis and management of atopic dermatitis (AD). This continuing education activity is intended for physicians, physician assistants, nurse practitioners, and nurses with an interest in skin and wound care. After completing this continuing education activity, you should be able to:1. Recall the diagnostic process of AD.2. Identify nonpharmacologic therapies for skin care in patients with AD.3. Explain the pharmacologic management of AD. Atopic dermatitis is a chronic, relapsing, intensely pruritic inflammatory skin disease that affects both children and adults. This article provides an overview of the epidemiology, clinical features, pathophysiology, complications, and specific investigations of atopic dermatitis. The current and novel therapies for the treatment of atopic dermatitis will be discussed.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/30475283/</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>41014074</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Preventive and curative approaches to diaper dermatitis in children: a systematic review.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Octarica SG; Ellistasari EY; Dewi AK; Sambodo SL; Utama RFD; Adjie SP</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Acta dermatovenerologica Alpina, Pannonica, et Adriatica</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Diaper dermatitis (DD) is a common inflammatory skin condition in the diaper area of infants, caused by a combination of host and environmental factors, such as moisture, friction, elevated skin pH, and prolonged exposure to urine and feces. This systematic review analyzed 13 studies involving 2,935 children to evaluate effective treatment and prevention strategies for DD. Key interventions identified include the use of disposable and emollient-containing diapers, gentle skincare practices (such as bathing every 1 to 2 days with mild cleansers and emollients), and pH-balanced wet wipes. Frequent diaper changes and allowing diaper-free time also help reduce skin irritation. Topical treatments, particularly emollients with zinc oxide or dexpanthenol, were found to be highly effective with minimal side effects. Preventive measures, such as using superabsorbent disposable diapers, regular application of barrier creams, and maintaining good hygiene, are crucial in reducing the incidence and severity of DD. In conclusion, a combined approach of proper diaper selection, gentle skincare, and judicious use of topical emollients is recommended for both treatment and prevention of DD in children.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41014074/</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.6492</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>34280477</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Management of Pediatric Atopic Dermatitis by Primary Care Providers: A Systematic Review.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Young TK; Glick AF; Yin HS; Kolla AM; Velazquez JJ; Nicholson J; Oza VS</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Academic pediatrics</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>10.1016/j.acap.2021.07.008</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Primary care providers (PCPs), including pediatricians and general practitioners, are often the first to see children with eczema/atopic dermatitis (AD). Little is known about management of pediatric AD by PCPs and adherence to national guidelines. To review existing literature examining management components of pediatric AD (topical corticosteroids [TCS], topical calcineurin inhibitors [TCIs], antihistamines, bathing, emollients, and diet) by PCPs. PubMed/Medline and Embase. English-language articles dated 2015 to 2020 reporting outcomes addressing management of pediatric AD by PCPs. Two authors independently screened titles/abstracts, reviewed full-text articles, extracted relevant data, and evaluated study quality. Disagreements were resolved by a third author. Twenty articles were included. Surveys and national database analyses were the most common methodologies (n = 7 each). PCPs commonly prescribed TCS but had a preference for low-potency agents, overprescribed nonsedating antihistamines, and avoided TCIs. PCPs commonly recommended emollients, although this was not universal. Data characterizing nonmedication management were limited. Most studies did not examine individual patient encounters, but rather relied on providers reporting their general behaviors. Provider behavior may vary based on country of practice. Knowledge and management gaps exist among PCPs in treating pediatric AD in key areas including knowledge of TCS safety profiles and prescribing of TCIs. The current literature is largely limited to small studies that evaluate prescribing behaviors with limited data characterizing nonmedication management, highlighting the need for future research in this area.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34280477/</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.6472</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>34779023</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Pharmacological interventions for periorificial (perioral) dermatitis in children and adults: a systematic review.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Gray NA; Tod B; Rohwer A; Fincham L; Visser WI; McCaul M</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Journal of the European Academy of Dermatology and Venereology : JEADV</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>10.1111/jdv.17817</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>The plethora of pharmacologic treatments used for periorificial dermatitis (POD) makes clinical decision-making challenging. The objectives of this review were to assess the efficacy and safety of pharmacological interventions for POD in children and adults. The search was performed on 2 February 2021 and included seven databases and trial registries, with no date or language restrictions Study selection, data extraction and risk of bias assessments were performed independently and in duplicate by two authors, in accordance with a prespecified protocol. Meta-analyses were performed and reported in accordance with PRISMA guidelines. Where meta-analysis was not possible, a narrative synthesis was performed and reported in accordance with SWiM guidelines. The certainty of evidence was assessed using the Grading of Recommendation, Assessment, Development and Evaluation approach. Eleven studies representing 733 participants were included. Oral tetracycline may improve physician-reported severity of POD from day 20 onwards (low certainty evidence). Adverse effects may include abdominal discomfort, facial dryness and pruritus. Pimecrolimus cream may improve physician-reported severity slightly after 4 weeks of treatment (MD -0.49, 95% CI -1.02 to 0.04, n = 164, low certainty evidence). Adverse effects may include erythema, herpes simplex virus infection, burning and pruritus. Azelaic acid gel may result in no change in either physician- or patient-reported severity after 6 weeks of treatment. The evidence is very uncertain about the effect of praziquantel ointment on physician-reported severity and skin-related quality of life after 4 weeks of treatment. The evidence is also very uncertain about the effect of topical clindamycin/benzoyl peroxide on physician-reported severity. The body of evidence to inform treatment of POD currently consists of low and very low certainty evidence for important outcomes. Well-designed trials are needed to further investigate treatment options. Data are required for children and from low-middle income countries to improve external validity. Future trials should also include adequate post-treatment follow-up and standardized outcome measures.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34779023/</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.644</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>27141486</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>A review on the role of moisturizers for atopic dermatitis.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Giam YC; Hebert AA; Dizon MV; Van Bever H; Tiongco-Recto M; Kim KH; Soebono H; Munasir Z; Diana IA; Luk DC</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Asia Pacific allergy</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>10.5415/apallergy.2016.6.2.120</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Effective management of atopic dermatitis (AD) involves the treatment of a defective skin barrier. Patients with AD are therefore advised to use moisturizers regularly. To date, there are few comparative studies involving moisturizers in patients with AD, and no classification system exists to objectively determine which types of moisturizers are best suited to specific AD phenotypes. With this in mind, a group of experts from allergy and immunology, adult and pediatric dermatology, and pediatrics centers within Southeast Asia met to review current data and practice, and to develop recommendations regarding the use of moisturizers in patients with AD within the Asia-Pacific region. Chronicity and severity of AD, along with patient age, treatment compliance, and economic background should all be taken into account when selecting an appropriate moisturizer for AD patients. Other considerations include adjuvant properties of the product, cosmetic acceptability, and availability over the counter. Well-defined clinical phenotypes of AD could optimally benefit from specific moisturizers. It is hoped that future studies may identify such differences by means of filaggrin mutation subtypes, confocal microscopic evaluation, pH, transepidermal water loss or presence of allergy specific IgE. Recommendations to improve the regular use of moisturizers among AD patients include measures that focus on treatment compliance, patient and caregiver education, appropriate treatment goals, avoidance of sensitizing agents, and collaboration with other relevant specialists.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/27141486/</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.6433</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>41949509</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Guidelines of care for the primary prevention of atopic dermatitis and awareness of comorbid conditions in pediatric atopic dermatitis.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sidbury R; Alikhan A; Bercovitch L; Cohen DE; Darr JM; Drucker AM; Eichenfield LF; Frazer-Green L; Paller AS; Schwarzenberger K; Silverberg JI; Singh AM; Wu PA; Davis DMR</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Journal of the American Academy of Dermatology</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>10.1016/j.jaad.2026.02.114</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Pediatric atopic dermatitis (AD) is a common, chronic inflammatory skin disorder that significantly impacts the quality of life of affected children and their families. In addition to skin-related symptoms, AD in pediatric patients may be associated with a range of comorbid conditions. To provide evidence-based recommendations on primary prevention of AD and to appraise evidence of the association between AD and comorbidities among pediatric patients. A multidisciplinary workgroup conducted a systematic review and applied the Grading of Recommendations, Assessment, Development, and Evaluation approach for assessing the certainty of evidence and formulating and grading recommendations. The workgroup developed 14 evidence-based recommendations on primary prevention of AD and 29 statements on the association between pediatric AD and comorbid conditions. This analysis is based on the best available evidence at the time it was conducted. This guideline does not make recommendations for screening or management of comorbidities in children with AD. We make a conditional recommendation for moisturizing skin care to reduce the occurrence of AD and conditional recommendations against early food introduction, human milk consumption, and probiotic or vitamin D supplementation for the primary prevention of AD. Clinicians should be aware of comorbidities associated with pediatric AD, but further research is needed to optimize screening and/or management of comorbidities.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41949509/</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.6424</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>33400416</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>The ABC Topical Management of Atopic Dermatitis in Philippines: Expert Recommendations.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Lavadia AM; Cumagun AT; Palmero L; Ramos NS; Tan CJ</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Journal of drugs in dermatology : JDD</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>10.36849/JDD.5080</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis (AD) has been shown to have an increasing incidence in Asia, congruous with the trends observed worldwide. The severity of the condition has been associated with challenges in disease control. Moreover, a significant number of patients do not adhere to their physicians&amp;rsquo; recommendations correctly and prefer alternative treatments. Better education regarding the nature of the disease and its appropriate management may improve patient compliance and lead to better control. An ABC scheme of AD management entails anti-inflammatory, barrier repair and basic skin care strategies to adequately manage AD. It is an easy-to-follow model which helps lessen distress and improve the quality of life amongst patients. An expert panel composed of specialists in the field of dermatology and pediatric dermatology in the Philippines convened to review current data and management practices in order to provide key treatment recommendations and identify current gaps in the treatment of mild to moderate atopic dermatitis. This scientific expert panel, likewise, seeks to provide guidance for all healthcare professionals involved in the care and management of AD patients.J Drugs Dermatol. 2021;20(1):84-87. doi:10.36849/JDD.5080.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/33400416/</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>33177843</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Current Perspectives on the Management of Infantile Atopic Dermatitis.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Davari DR; Nieman EL; McShane DB; Morrell DS</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Journal of asthma and allergy</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>10.1016/j.jaad.2018.06.047</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis (AD) is a common disease of childhood, and infantile AD may manifest from birth to 2 years. Guidelines for the management of infantile AD are lacking, and our aim is to provide a comprehensive review of best practices and possible interventions. We will focus on topical therapy, since the use of systemic immunomodulating agents in infantile AD is rarely advised. Topical agents include emollients, topical corticosteroids (TCS), topical calcineurin inhibitors (TCIs), and phosphodiesterase 4 (PDE-4) inhibitors. We will also provide a brief overview of promising emerging therapies currently under investigation in the pediatric population.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/33177843/</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.6397</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>37605504</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Insights into acne and the skin barrier: Optimizing treatment regimens with ceramide-containing skincare.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Schachner LA; Alexis AF; Andriessen A; Berson D; Gold M; Goldberg DJ; Hu S; Keri J; Kircik L; Woolery-Lloyd H</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Journal of cosmetic dermatology</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>10.1111/jocd.15946</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Acne is a common, complex, multifactorial inflammatory skin disease associated with epidermal barrier dysfunction. Beginning in childhood, acne affects many adolescents and adults. Acne is associated with lower self-esteem, anxiety, and depression and may cause scars and pigmentary sequelae. The review explores the relationships between acne and the skin barrier function and discusses nuances in the prevention, treatment, and maintenance of acne and its impact on the skin barrier. The advisors' previous publications addressed prescription and nonprescription pediatric acne treatment and skincare using cleansers, moisturizers, and a practical algorithm for treatment and maintenance, including skincare recommendations for pediatric acne patients and an algorithm for skin of color patients with acne. Before the meeting, literature was culled on the relationship between the skin barrier and acne and current best practices in acne, addressing prescription and nonprescription acne products and skincare as monotherapy, adjunctive, and maintenance treatment. After discussing 13 draft statements, the advisors applied the selected literature and drew from their clinical knowledge and experience, and agreed on five statements. The follicular epithelial barrier is directly involved with changes that occur during both comedogenesis and in stages of inflammation, especially with follicular rupture compromising the barrier's integrity. In acne-affected skin, sebaceous glands are larger, sebum excretion and filaggrin expression higher, and stratum corneum lipids are reduced. Educating patients and clinicians about inflammation's central role in acne and measures to reduce inflammation is essential. Skin irritation and xerosis from acne and treatments lead to poor treatment adherence. A skincare regimen should be included in the acne prevention, treatment, and maintenance care regimen and should be ongoing. Maintenance treatment with topical agents and skincare using gentle ceramide-containing cleansers and moisturizers is a recommended strategy after successfully controlling the disease. Epidermal barrier dysfunction contributes to acne exacerbation. Using the appropriate treatment and skincare helps to minimize irritation and inflammation, enhance treatment adherence, and improve patient outcomes.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37605504/</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.6389</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>30608338</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Prevention and Management of Incontinence-Associated Dermatitis in the Pediatric Population: An Integrative Review.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Lim YSL; Carville K</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Journal of wound, ostomy, and continence nursing : official publication of The Wound, Ostomy and Continence Nurses Society</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>10.1097/WON.0000000000000490</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>An integrative review was conducted to synthesize evidence on prevention and management of incontinence-associated dermatitis (IAD) in the pediatric population. A 5-step integrative process was used to guide the review. Articles published from January 2000 to April 6, 2017, were identified and retrieved from CINAHL, PubMed, ProQuest (MEDLINE), and Scopus; key terms were associated with IAD, pediatric, prevention, and management. Supplemental and manual searches were carried out to identify other relevant studies. The studies' findings were extracted and summarized in a table of evidence, with their quality evaluated using the Joanna Briggs Institute's Critical Appraisal Checklist. Sixteen articles were included in the review. Articles explored prevention and management strategies including skin cleansing technique, diaper selection, and the application of topical skin care products. Inconsistent and limited evidence was found regarding the benefits of using disposable wipes in preference to water-moistened washcloths in the cleansing process and on the use of superabsorbent polymer diapers with breathable outer lining in IAD prevention. Findings were inconclusive with regard to the best topical skin care product for IAD care. However, the application of skin protectants was encouraged by the authors, as well as promoted in various clinical guidelines. The development of a structured skin care regimen supplemented by a comprehensive patient education program was advised to enhance the prevention and management of IAD.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/30608338/</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.6381</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>34784132</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>The Importance of Skincare for Neonates and Infants: An Algorithm.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Schachner L; Andriessen A; Benjamin L; Bree A; Lechman P; Pinera-Llano A; Kircik L; Hebert A</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Journal of drugs in dermatology : JDD</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>10.36849/jdd.6219</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>The skin of neonates and infants undergoes a maturation process from birth and is susceptible to barrier disruption. The current algorithm follows a US-based consensus paper on skincare approaches using gentle cleansers and moisturizers in neonatal and healthy infant skin. This summary provides clinical information for pediatric dermatologists, dermatologists, and pediatric healthcare providers treating neonates and infants. The project used a modified Delphi process comprising virtual discussions followed by an online follow-up replacing the use of a questionnaire. During the virtual meeting, the systematic literature review results and a draft algorithm addressing over-the-counter skincare for neonates and infants with healthy skin were discussed and adopted using evidence coupled with the expert opinion and experience of the panel. The algorithm addresses three clinical signs: xerosis, erythema, and erosion/bulla. A growing body of evidence recognizes the benefits of ongoing daily use of non-alkaline cleansers and ceramides containing moisturizers to reduce inflammation and maintain a healthy skin barrier function. Diaper rash is common in infants presenting as erythema or, in more severe cases, skin erosion. Skin protection with a barrier cream and frequent diaper changes using disposable diapers resolves most cases; however, if the rash continuous despite appropriate care, rule out a candida infection. The current algorithm focuses on neonatal and infant healthy skin that can benefit from skincare. When applied from birth onwards, gentle cleansers and moisturizers containing barrier lipids help maintain the protective skin barrier. J Drugs Dermatol. 2021;20(11):1195-1205. doi:10.36849/JDD.6219.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34784132/</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0.6356000000000001</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>41769510</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Clinical Effectiveness of Barrier Preparations in the Management of Diaper Dermatitis: A Systematic Review and Meta-Analysis.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Alkhamis ZZ; Bhagchandani M; Idris M; Bhyat Y; Alsani SM; Pasha AI; Ali AHA; Ali Eledresi D; Mahdi AA; Almohamedhusain FR</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>10.7759/cureus.102379</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>The inflammatory skin condition known as diaper dermatitis (DD) often affects infants and preschoolers. Barrier preparations are commonly used in their management, but their effectiveness remains unclear. This systematic review aimed to evaluate the extent to which barrier preparations reduce DD compared to a placebo or other therapies. To gather relevant information, we conducted electronic searches on databases such as Medical Literature Analysis and Retrieval System Online (MEDLINE) via PubMed, Scopus, Web of Science, Cochrane Central Register of Controlled Trials (CENTRAL), and Google Scholar for data extraction. We included studies based on randomized controlled trials (RCTs), quasi-randomized controlled studies, and cohort studies. The collected data were analyzed using RevMan version 5.3 (The Cochrane Collaboration, London, United Kingdom) for Windows. This study included a total of six studies, comprising four randomized controlled trials and two cohort studies. The analysis focused on the incidence rates of dermatitis among both experimental and placebo groups across approximately four studies. A significant difference in dermatitis prevalence was observed between the intervention and placebo groups (odds ratio {ORs} = 0.77; confidence interval {CI} = 0.37-1.61; p = 0.0002), with notable heterogeneity noted (degrees of freedom {df} = 3; I</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41769510/</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0.6353</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>40907991</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Prevention of Atopic Dermatitis in High-Risk Infants: A Review of the Role of Lipid-Based Barrier Repair Therapy.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Chan CJ; Visscher MO</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pediatric dermatology</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>10.1111/pde.70010</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Growing evidence highlights the role of physiological lipids, namely ceramides, cholesterol, and free fatty acids, in maintaining skin barrier function and preventing atopic dermatitis (AD). Current evidence on the efficacy, safety, and clinical relevance of stratum corneum (SC) lipid-based therapies to prevent AD and increase skin barrier integrity in high-risk infants was reviewed and synthesized. Searches with key words lipid-based therapy, atopic dermatitis, infant, and prevention were conducted to identify papers using PubMed, Embase, Cochrane Library, and Scopus databases from January 2000 to June 2024. SC lipid-based therapies were reported to replenish deficient SC lipids, thereby improving skin barrier function, a critical aspect of AD management. These therapies reduced SCORAD scores, enhanced hydration, and improved epidermal cohesion, with some studies reporting comparable efficacy to topical corticosteroids when used as adjunct treatments. However, evidence supporting their effectiveness in preventing AD onset in infants remains limited, with only trends toward reduced AD incidence and food sensitization reported, without statistical significance. Importantly, SC lipid therapies are well tolerated, with no significant adverse effects noted, supporting their safety in infants and children. This review ascertained knowledge gaps that can direct research and resolve controversies regarding emollients. Mechanistic studies in high-risk and non-atopic infants, starting at birth, are warranted using within-subject comparisons and frequent evaluations, including SC sampling for proteomics and lipidomics outcomes for mechanistic insight. Studies should begin with relatively simple formulations, for example, containing only ceramides, cholesterol, and fatty acids matched to varying infant SC lipid profiles at birth and over time.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40907991/</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0.6339</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>30058384</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Investigational drugs for atopic dermatitis.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Hon KL; Leung AKC; Leung TNH; Lee VWY</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Expert opinion on investigational drugs</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>10.1080/13543784.2018.1494723</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Many novel medications and herbal medicines have claimed efficacy on atopic dermatitis (AD). This review covers evidence on efficacy of topical and oral forms of novel and investigational drugs. Topical agents include emollients, phosphodiesterase E4 (PDE4) inhibitors, and topical herbs. There is little evidence that ceramides or natural moisturizing factors provide relief in AD. PDE4 inhibitors have shown promise as an effective topical treatment for mild-to-moderate AD with minimal adverse events, and dupilumab as an effective subcutaneous agent for the treatment of moderate-to-severe AD in adult patients with little adverse effects. However, only preliminary data are available for dupilumab in children with AD. The long-term effects of dupilumab are also not known. Potential new systemic treatments include a number of herbal concoctions. Randomized, double-blind placebo-controlled trials (RCTs) have demonstrated topical PDE4 inhibitors are effective and safe in the treatment of both children and adults with AD but further evaluations are needed. RCTs have also shown that subcutaneous dupilumab is an effective and safe agent for the treatment of AD in adults. Long-term effects of these topical and systemic investigational drugs are currently unavailable. Regarding herbal medications, scientific methods are often flawed and objective evidence is lacking.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/30058384/</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.633</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>36131640</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Reducing costs in atopic dermatitis.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Myers EM; Perche PO; Jorizzo JL; Feldman SR</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Dermatologic therapy</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>10.1111/dth.15849</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis (AD) is a common relapsing inflammatory skin condition associated with a high economic burden due to its chronicity and multitude of direct and indirect treatment costs. AD disproportionately impacts children and minority populations, and treatment choices are cost-prohibitive for many patients. Our objective was to describe the treatment and management of AD from a cost-conscious perspective. A review of the literature was conducted with PubMed using the following keywords: AD, cost, medications, treatment, management, efficacy, adherence, education, and prophylactic. The use of moisturizers prophylactically in high-risk infants who have yet to develop AD may reduce incidence of disease and associated costs. Increasing patient medication adherence and moisturizing between flares also reduces costs in AD. The use of corticosteroids as the first-line treatment is efficacious and cost-effective for mild cases of AD, however, in severe cases of AD corticosteroids alone are not sufficient. Systemic biologics are necessary in some patients with severe cases of AD; however, they are associated with high costs. Phototherapy, through portable home units, tanning beds, and natural sunlight are cost-effective alternatives. Effective management of AD improves with education programs for both the patient and their family, reducing long-term costs in the management of this disease. Reducing AD treatment costs requires consideration of prophylactic therapies, patient education, and should differ based on the severity of disease. A multifaceted approach to AD treatment reduces costs and health-care barriers.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/36131640/</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0.629</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>33026767</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Topical Agents Currently in Phase II or Phase III Trials for Atopic Dermatitis.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Uppal SK; Chat VS; Kearns DG; Wu JJ</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Journal of drugs in dermatology : JDD</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>10.36849/JDD.2020.5214</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Mild to moderate atopic dermatitis (AD) occurs frequently in children and adults and is usually managed through the use of pharmacologic treatments, such as topical corticosteroids (TCS) and topical calcineurin inhibitors (TCIs), and good skin care practices. As chronic TCS or TCI can lead to the development of adverse effects, there is a need for safe, alternative treatments for patients with resistant AD. A systemic literature review was performed to examine the safety and efficacy of topical agents currently in phase II and phase III clinical trials for AD. Our team searched the databases, PubMed, Google Scholar, and ClinicalTrials.gov, on March 2020 for studies pertaining to the use of topical agents in AD. Key words included each drug (tapinarof, crisaborole, ARQ-151 cream, ruxolitinib) or "topical agents"; combined with "atopic dermatitis"; Articles published within the last 5 years were included as references. References within retrieved articles were also reviewed to identify potentially missed studies. A total of 24 articles were included in this review. Tapinarof, crisaborole, and ruxolitinib lead to statistically significant improvements in multiple disease severity scores. ARQ-151 cream achieved statistical significance in secondary endpoints, including vIGA-AD and EASI-75, but not in the primary endpoint of the study. All topical agents were well-tolerated by study participants. The findings demonstrate that tapinarof, crisaborole, ARQ-151 cream, and ruxolitinib are safe, effective treatment options for patients with mild to moderate AD. J Drugs Dermatol. 2020;19(10):956-959. doi: 10.36849/JDD.2020.5214.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/33026767/</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0.6282</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>38625386</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>The use of essential oils in atopic dermatitis: a review.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Azhari H; Ng SF; Mohd Razali R; Loo HL</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Current medical research and opinion</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>10.1080/03007995.2024.2340734</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis (AD) has become a common childhood disease that affects a large number of children worldwide and has become a chronic skin disease that causes huge economical and psychological damage to the whole family. Despite the use of steroids, immunosuppressants, and various topical preparation, the prognosis is still poor. Hence, this review aimed to explore the potential of using essential oils (EO) as an active ingredient in managing AD. The review was completed by using Pubmed, Scopus, and Medline to search for relevant articles that study the pathophysiology of AD, the properties of EO, the use of EO in managing AD, and the suitable advanced formulation to incorporate EO. From the review conducted, it was concluded that EO have huge potential in managing AD and can be used as complimentary therapeutic agents in AD treatment. Scientists and industries should venture into commercializing more topical products with EO to help manage AD more effectively.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/38625386/</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.6256</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>34424533</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Moisturisers from birth in at-risk infants of atopic dermatitis - a pragmatic randomised controlled trial.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Ng PSM; Wee LWY; Ho VPY; Tan WC; Bishnoi P; Alagappan U; Wong SMY; Gan EY; Quek BH; Shen L; Su B; Common JE; Koh MJA</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>The Australasian journal of dermatology</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>10.1111/j.1365-2133.2011.10331.x</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis (AD) is a common, chronic dermatosis, with onset of disease often manifesting in early infancy. Past studies evaluating the early use of moisturisers in the prevention of AD had mixed results. To compare the incidence of moderate or severe AD and total incidence of AD in a cohort of 'at-risk' infants treated with moisturisers from the first 2 weeks of life, to a similar group without moisturisers. We performed a single-centre, prospective, parallel-group, randomised study in infants with at least 2 first-degree relatives with atopy. Subjects were randomised into either a treatment group with moisturisers or a control group without moisturisers. Participants were assessed at 2, 6, and 12 months for AD and if present, the severity was assessed using SCORAD index. We also compared the overall incidence of AD, trans-epidermal water loss (TEWL), stratum corneum (SC) hydration, pH, and incidence of food and environmental sensitisation and allergies between both groups. Genotyping for loss-of-functions mutations in the FLG gene was conducted. A total of 200 subjects were recruited, with 100 subjects in each arm. There was no significant difference in incidence of moderate or severe AD, and total incidence of AD at 12 months between the treatment and control groups. There was a lower mean SCORAD in the treatment group than in the control group, but no significant difference in TEWL, SC hydration, and skin pH. No significant side-effects were reported. The early use of moisturisers in 'at-risk' infants does not reduce the incidence of moderate-to-severe AD and overall incidence of AD in infancy.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34424533/</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.6243</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>31584781</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>A Global Review on the Risk Factors and Management of Early Atopic Dermatitis in Children Ages 0 to 2 Years Old.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Journal of drugs in dermatology : JDD</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Introduction: Atopic dermatitis (AD) is a chronic, relapsing skin disease starting typically in atopic-prone children between 3–6 months of age, with most children having developed AD by the age of 5 years. Intense itching leads to sleep disturbance, especially in younger children and toddlers. This review explores early intervention in infants and young children with AD by controlling skin barrier function and inflammation at the earliest time point using a moisturizer and a proactive treatment. Methods: A working group of experienced clinicians managing pediatric populations with AD convened for a meeting. The panel reviewed the literature surrounding early intervention in infants and young children with AD and developed and discussed clinical questions aimed at optimizing clinical outcomes. Results: Complex gene/immune system/environment interactions are involved in AD development. Epidermal barrier defects play a central role in the condition, with various studies showing impairment of skin barrier function at birth may precede clinical AD. Dynamic changes take place in the amounts of skin lipids during infancy. Studies confirm that daily use of a moisturizer from birth onwards may offer benefits in improving skin barrier function and possibly prevention of AD, especially in high-risk, atopic prone newborns. Plant-based moisturizers were shown to be safe and effective when applied in pediatric patients with AD and may provide a TCS-sparing effect while improving skin condition. Conclusion: Dry skin conditions during infancy may predict the subsequent development of AD. Consequently, emollient therapy from birth represents a feasible, safe, and effective approach for AD prevention. Therefore, parental education and the application of moisturizers are recommended as an integral part of AD prevention, treatment, and maintenance. J Drugs Dermatol. 2019;18(10):1020-1027.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/31584781/</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.6236</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>38832936</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Neonatal skin health and associated dermatological conditions.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Rezaei SJ; Linggonegoro D; Admani S</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Current opinion in pediatrics</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>10.1097/MOP.0000000000001372</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>This review describes recent developments in neonatal skincare management and situates these findings within the preexisting literature on neonatal dermatology. The studies included in this review expand research methods evaluating skincare management to different contexts across the world. Several studies explore the roles of emollient therapy, disinfection, and skin-to-skin contact on improving neonates' long-term health outcomes. Recent findings also assess the impact of neonatal interventions on atopic dermatitis risk later in life as well as epidemiological and microbiome variables that may predict this risk. Additionally, updates on various dermatological conditions unique to neonates are discussed in further detail. Neonatal skincare management differs in notable ways from that of other age groups. The presentation of dermatologic diseases as well as the rare conditions that affect neonates make their clinical management unique. The recent literature on neonatal dermatology can help inform clinicians regarding important considerations in treating their neonatal population.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/38832936/</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.6231</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>28071289</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[Local barrier creams for skin care in newborns, infants and toddlers with incontinence-associated dermatitis (IAD) – Narrative Review].</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Reick S; Hubenthal N; Zimmermann M; Hering T</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Pflege</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>10.1024/1012-5302/a000522</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Background: The incontinence-associated dermatitis (IAD) is a common condition in newborns, infants and toddlers. For the therapy nurses and parents have the choice between numerous barrier creams based on zinc oxide, Dexpanthenol or Vaseline in various combinations of active agents and with additional ingredients. Research question: Which combination of active ingredients in local barrier creams reduce pain, severity of or duration of healing in IAD in neonates, infants and young children? Method: MEDLINE and CINAHL was systematically search for randomized controlled trials on the effect of barrier creams in pediatric patients with IAD. These were evaluated on validity and applicability. Results: 15 RCTs were found, of which six were included in the systematic review. The methodological quality of these trials ranges from good to poor, partially high bias risk were recognizable. Barrier creams containing the active ingredients zinc oxide / lanolin, zinc oxide / cod liver oil, zinc oxide / Dexpanthenol, paraffin / beeswax / Dexpanthenol show effects. They reduce the IAD-associated symptoms. Conclusions: The investigated barrier creams can be used in the pediatric nursing for the treatment of IAD. Because of limitations it cannot be ruled out that further studies will change the results.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/28071289/</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.6222</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>39132734</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Educational and psychological interventions for managing atopic dermatitis (eczema).</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Singleton H; Hodder A; Almilaji O; Ersser SJ; Heaslip V; O'Meara S; Boyers D; Roberts A; Scott H; Van Onselen J; Doney L; Boyle RJ; Thompson AR</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>The Cochrane database of systematic reviews</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>10.1002/14651858.CD014932</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis (eczema), can have a significant impact on well-being and quality of life for affected people and their families. Standard treatment is avoidance of triggers or irritants and regular application of emollients and topical steroids or calcineurin inhibitors. Thorough physical and psychological assessment is central to good-quality treatment. Overcoming barriers to provision of holistic treatment in dermatological practice is dependent on evaluation of the efficacy and economics of both psychological and educational interventions in this participant group. This review is based on a previous Cochrane review published in 2014, and now includes adults as well as children. To assess the clinical outcomes of educational and psychological interventions in children and adults with atopic dermatitis (eczema) and to summarise the availability and principal findings of relevant economic evaluations. We searched the Cochrane Skin Specialised Register, CENTRAL, MEDLINE, Embase, APA PsycINFO and two trials registers up to March 2023. We checked the reference lists of included studies and related systematic reviews for further references to relevant randomised controlled trials (RCTs) and contacted experts in the field to identify additional studies. We searched NHS Economic Evaluation Database, MEDLINE and Embase for economic evaluations on 8 June 2022. Randomised, cluster-randomised and cross-over RCTs that assess educational and psychological interventions for treating eczema in children and adults. We used standard Cochrane methods, with GRADE to assess the certainty of the evidence for each outcome. Primary outcomes were reduction in disease severity, as measured by clinical signs, patient-reported symptoms and improvement in health-related quality-of-life (HRQoL) measures. Secondary outcomes were improvement in long-term control of symptoms, improvement in psychological well-being, improvement in standard treatment concordance and adverse events. We assessed short- (up to 16 weeks after treatment) and long-term time points (more than 16 weeks). We included 37 trials (6170 participants). Most trials were conducted in high-income countries (34/37), in outpatient settings (25/37). We judged three trials to be low risk of bias across all domains. Fifteen trials had a high risk of bias in at least one domain, mostly due to bias in measurement of the outcome. Trials assessed interventions compared to standard care. Individual educational interventions may reduce short-term clinical signs (measured by SCORing Atopic Dermatitis (SCORAD); mean difference (MD) -5.70, 95% confidence interval (CI) -9.39 to -2.01; 1 trial, 30 participants; low-certainty evidence) but patient-reported symptoms, HRQoL, long-term eczema control and psychological well-being were not reported. Group education interventions probably reduce clinical signs (SCORAD) both in the short term (MD -9.66, 95% CI -19.04 to -0.29; 3 studies, 731 participants; moderate-certainty evidence) and the long term (MD -7.22, 95% CI -11.01 to -3.43; 3 studies, 1424 participants; moderate-certainty evidence) and probably reduce long-term patient-reported symptoms (SMD -0.47 95% CI -0.60 to -0.33; 2 studies, 908 participants; moderate-certainty evidence). They may slightly improve short-term HRQoL (SMD -0.19, 95% CI -0.36 to -0.01; 4 studies, 746 participants; low-certainty evidence), but may make little or no difference to short-term psychological well-being (Perceived Stress Scale (PSS); MD -2.47, 95% CI -5.16 to 0.22; 1 study, 80 participants; low-certainty evidence). Long-term eczema control was not reported. We don't know whether technology-mediated educational interventions could improve short-term clinical signs (SCORAD; 1 study; 29 participants; very low-certainty evidence). They may have little or no effect on short-term patient-reported symptoms (Patient Oriented Eczema Measure (POEM); MD -0.76, 95% CI -1.84 to 0.33; 2 studies; 195 participants; low-certainty evidence) and probably have little or no effect on short-term HRQoL (MD 0, 95% CI -0.03 to 0.03; 2 studies, 430 participants; moderate-certainty evidence). Technology-mediated education interventions probably slightly improve long-term eczema control (Recap of atopic eczema (RECAP); MD -1.5, 95% CI -3.13 to 0.13; 1 study, 232 participants; moderate-certainty evidence), and may improve short-term psychological well-being (MD -1.78, 95% CI -2.13 to -1.43; 1 study, 24 participants; low-certainty evidence). Habit reversal treatment may reduce short-term clinical signs (SCORAD; MD -6.57, 95% CI -13.04 to -0.1; 1 study, 33 participants; low-certainty evidence) but we are uncertain about any effects on short-term HRQoL (Children's Dermatology Life Quality Index (CDLQI); 1 study, 30 participants; very low-certainty evidence). Patient-reported symptoms, long-term eczema control and psychological well-being were not reported. We are uncertain whether arousal reduction therapy interventions could improve short-term clinical signs (Eczema Area and Severity Index (EASI); 1 study, 24 participants; very low-certainty evidence) or patient-reported symptoms (visual analogue scale (VAS); 1 study, 18 participants; very low-certainty evidence). Arousal reduction therapy may improve short-term HRQoL (Dermatitis Family Impact (DFI); MD -2.1, 95% CI -4.41 to 0.21; 1 study, 91 participants; low-certainty evidence) and psychological well-being (PSS; MD -1.2, 95% CI -3.38 to 0.98; 1 study, 91 participants; low-certainty evidence). Long-term eczema control was not reported. No studies reported standard care compared with self-help psychological interventions, psychological therapies or printed education; or adverse events. We identified two health economic studies. One found that a 12-week, technology-mediated, educational-support programme may be cost neutral. The other found that a nurse practitioner group-education intervention may have lower costs than standard care provided by a dermatologist, with comparable effectiveness. In-person, individual education, as an adjunct to conventional topical therapy, may reduce short-term eczema signs compared to standard care, but there is no information on eczema symptoms, quality of life or long-term outcomes. Group education probably reduces eczema signs and symptoms in the long term and may also improve quality of life in the short term. Favourable effects were also reported for technology-mediated education, habit reversal treatment and arousal reduction therapy. All favourable effects are of uncertain clinical significance, since they may not exceed the minimal clinically important difference (MCID) for the outcome measures used (MCID 8.7 points for SCORAD, 3.4 points for POEM). We found no trials of self-help psychological interventions, psychological therapies or printed education. Future trials should include more diverse populations, address shared priorities, evaluate long-term outcomes and ensure patients are involved in trial design.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39132734/</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0.6221</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>41630239</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Efficacy of combining soothing moisturizing repairing cream with glucocorticoids in the treatment of moderate atopic dermatitis in pediatric patients: A prospective observational cohort study.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Guan Z; Lin Y; Wang Y; Chen L; Li Q</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Medicine</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>10.1097/MD.0000000000047171</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Glucocorticoids are the most commonly used drugs for the treatment of atopic dermatitis (AD) in children, this study aimed to explore the therapeutic efficacy of combining moisturizers and glucocorticoids in the treatment of moderate AD in pediatric patients. Patients aged 6 to 12 years with moderate AD were involved. The control group received fluticasone propionate cream twice daily, and the experimental group received soothing moisturizing repairing cream combined to the fluticasone. Both groups treated continuously for most 4 weeks until the Symptom Score Reduction Index ≥90% and then entered a 2-week remission phase. Clinical outcomes, fluticasone dosage, Children's Dermatology Life Quality Index, AD recurrence rates, remission duration, and adverse events were compared at the end of the remission period. A total of 54 patients completed the follow-up, with 25 in the control and 29 in the experimental group. The overall clinical efficiency in the experimental group (100%, 95% confidence interval: 88.1-100.0%) was significantly higher than in the control group (84%, 95% confidence interval: 63.9-95.5%) with P = .040. Both groups showed a decrease in Children's Dermatology Life Quality Index. The recurrence rate was remarkably lower, and the remission duration was longer in the experimental group (both P &lt; .05). Combining soothing moisturizing repairing cream with fluticasone cream has good clinical efficacy in the treatment of moderate AD in children. This combination therapy can effectively reduce the risk of relapses during the remission period, improve clinical symptoms, and improve quality of life in children with AD.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41630239/</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0.621</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>30532792</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Dismissing the fallacies of childhood eczema management: case scenarios and an overview of best practices.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Hon KL; Leong KF; Leung TN; Leung AK</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Drugs in context</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>10.1001/jamadermatol.2016.5538</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Eczema or atopic dermatitis (AD) is a common relapsing childhood dermatologic illness. Treatment of AD is primarily topical with emollients and corticosteroid/calcineurin inhibitor, which is efficacious for the majority of patients. However, AD is often complicated and difficult to manage in many Asian cities. Effective therapy is impeded by fallacies in the following aspects: (1) mistrust and unrealistic expectations about Western medicine, (2) skin care and allergy treatment, (3) ambiguity about optimal bathing and moisturizing, (4) hesitation and phobias about the usage of adequate topical corticosteroid and immunomodulatory therapies, (5) food and aeroallergen avoidance and dietary supplementation, and (6) complementary and alternative therapies. Eleven anonymized case scenarios are described to illustrate issues associated with these fallacies. A literature review is performed and possible solutions to handle or dismiss these fallacies are discussed. The first step in patient care is to accurately assess the patient and the family to evaluate possible concerns, anxiety, and phobias that could impede therapeutic efficacy. Education about the disease should be individualized. Conflicting recommendations on the usage of topical steroid have a detrimental effect on management outcomes, which must be avoided.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/30532792/</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.6185</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>36586583</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Safety, pharmacokinetics, and efficacy of ruxolitinib cream in children and adolescents with atopic dermatitis.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Leung DYM; Paller AS; Zaenglein AL; Tom WL; Ong PY; Venturanza ME; Kuligowski ME; Li Q; Gong X; Lee MS</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Annals of allergy, asthma &amp; immunology : official publication of the American College of Allergy, Asthma, &amp; Immunology</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>10.1016/j.anai.2022.12.033</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Therapies for children with atopic dermatitis (AD) have safety and tolerability concerns that may limit long-term use. Ruxolitinib cream, a Janus kinase (JAK) inhibitor, is effective and well tolerated in adolescents and adults with AD. To analyze the safety and tolerability of ruxolitinib cream in pediatric patients. Pharmacokinetics and efficacy were also evaluated in this phase 1 study (NCT03257644). Patients aged 2 to 17 years with AD (affected body surface area 8%-20%; Investigator's Global Assessment score ≥2) were enrolled stepwise in 6 age-descending, strength-increasing cohorts to apply 0.5%, 0.75%, or 1.5% ruxolitinib cream twice daily for 28 days. Safety, pharmacokinetics, and efficacy were analyzed at baseline, week 2 (day 10), and week 4 (day 29). Among 71 patients, 44 (62.0%) had a baseline Investigator's Global Assessment score of 3; median (range) body surface area affected at baseline was 12.2% (1.7%-20.4%). Ruxolitinib cream was well tolerated, with 4 patients (5.6%) experiencing treatment-related adverse events (all grades 1/2). No clinically meaningful changes in mean chemistry or hematology values were observed, and no consistent pattern of change in bone biomarkers was detected. Mean plasma ruxolitinib levels within each cohort (range, 23.1-97.9 nM) were well below the half-maximal inhibitory concentration for thrombopoietin phosphorylation of STAT3 (281 nM). All cohorts experienced improvements in exploratory efficacy end points. Ruxolitinib cream was well tolerated in pediatric patients with AD, with no effect on blood counts or bone biomarkers. Mean plasma concentration was low. Efficacy was consistent with data from previous studies in adolescents and adults. ClinicalTrials.gov Identifier: NCT03257644.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/36586583/</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.6182</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>41040777</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Climate Change and Pediatric Skin Health: Emerging Threats, Innovations, and Equity Gaps.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Multani HK; Sraa KK; Abbas H; Gandhi S; San Juan LJ; Pan EH; Riedel F; Khan S</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>10.7759/cureus.91397</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Climate change poses unique dermatologic risks to children due to immature skin barrier function, weakened immune systems, and dependence on caregivers. Under stable environmental conditions, pediatric skin maintains homeostasis through balanced barrier function, microbiome diversity, and immune regulation. The changing climate disrupts these protective mechanisms through rising temperatures, air pollution, ultraviolet (UV) radiation, and adverse weather conditions. Research demonstrates these environmental stressors exacerbate atopic dermatitis (AD), infectious dermatoses, and infestations, all while disproportionately affecting marginalized communities. Current clinical approaches often fail to address the climate-related dimensions of pediatric skin disease, relying on traditional therapies without environmental adaptation. Emerging solutions, such as climate-resilient skincare formulations, teledermatology, and community-based interventions, show promise for more effective management. This review examines the pathophysiological effects of climate change on pediatric skin, evaluates current and emerging care strategies, and identifies critical gaps in the literature. Challenges include limited pediatric-specific climate research, healthcare disparities in vulnerable populations, and inadequate integration of dermatologic concerns into climate policy. Despite these barriers, advances in preventive dermatology and community-based interventions offer opportunities to improve outcomes. Future progress will depend on interdisciplinary efforts to develop climate-adaptive skin care frameworks that protect children's health in a dynamic world.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41040777/</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0.6167</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>38287763</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>The roles of ceramides and multivesicular emulsion (MVE) technology in atopic dermatitis: a narrative review.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Chng CC</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>The Medical journal of Malaysia</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis (AD) is a highly prevalent chronic inflammatory skin condition. In Malaysia, a prevalence of 13.4% was reported for children between one and six years of age, one of the highest prevalence rates of AD in Asia. Many guidelines recommended moisturisers as the mainstay of treatment strategy for AD. Selecting an effective and suitable moisturiser for people with AD plays a crucial role in avoiding acute exacerbation of AD and achieving remission. Given that an array of active ingredients and topical vehicles for moisturisers are available in the market, this review summarised the roles of ceramides and multivesicular emulsion (MVE) technology in managing AD to help guide treatment decisions. Ceramides are essential in maintaining the skin permeability barrier and hydration, modulating skin immunity through anti-inflammatory and antimicrobial defence system, and regulating cellular functions. Low levels and altered structures and composition of ceramides, compromised skin permeability barrier and increased transepidermal water loss were commonly observed in AD patients. Most clinical studies have shown that ceramidedominant moisturisers are safe and effective in adults and children with AD. MVE technology offers an attractive delivery system to replenish ceramides in the SC, repairing the compromised skin permeability barrier and potentially improving patient compliance. Recommending clinically proven therapeutic moisturisers with the right ingredients (level, ratio, structure and composition), alongside an effective sustained release delivery system, to AD patients is one key strategy to successful disease control and flare prevention, subsequently reducing the disease burden to patients, families and societies.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/38287763/</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0.6162</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>28792444</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Role of Microbial Modulation in Management of Atopic Dermatitis in Children.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Hulshof L; Van't Land B; Sprikkelman AB; Garssen J</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Nutrients</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>10.1111/all.12700</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>The pathophysiology of atopic dermatitis (AD) is multifactorial and is a complex interrelationship between skin barrier, genetic predisposition, immunologic development, skin microbiome, environmental, nutritional, pharmacological, and psychological factors. Several microbial modulations of the intestinal microbiome with pre- and/or probiotics have been used in AD management, with different clinical out-come (both positive, as well as null findings). This review provides an overview of the clinical evidence from trials in children from 2008 to 2017, aiming to evaluate the effect of dietary interventions with pre- and/or pro-biotics for the treatment of AD. By searching the PUBMED/MEDLINE, EMBADE, and COCHRANE databases 14 clinical studies were selected and included within this review. Data extraction was independently conducted by two authors. The primary outcome was an improvement in the clinical score of AD severity. Changes of serum immunological markers and/or gastrointestinal symptoms were explored if available. In these studies some dietary interventions with pre- and/or pro-biotics were beneficial compared to control diets in the management of AD in children, next to treatment with emollients, and/or local corticosteroids. However, heterogeneity between studies was high, making it clear that focused clinical randomized controlled trials are needed to understand the potential role and underlying mechanism of dietary interventions in children with AD.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/28792444/</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.6132</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>28730617</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Methotrexate for Severe Childhood Atopic Dermatitis: Clinical Experience in a Tertiary Center.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Dvorakova V; O'Regan GM; Irvine AD</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Pediatric dermatology</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>10.1111/pde.13209</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis (AD) affects up to 20% of children. Although the majority of patients are adequately controlled using emollients, topical corticosteroids, topical calcineurin inhibitors, or phototherapy, children with moderate to severe AD may require systemic treatment for control. The objective of the current study was to evaluate the efficacy and safety of methotrexate in children with severe AD attending a tertiary referral center. A retrospective chart review was undertaken of all children who received methotrexate for severe AD at our tertiary referral center from November 2010 to August 2015. Forty-seven children were started on methotrexate for AD during this period. The mean Investigator Global Assessment (IGA) at the 3- to 5-month follow-up improved from 4.25 to 2.8, with further improvement to 1.9 in the patients that continued therapy beyond 10 months. Changes in the Children's Dermatology Life Quality Index (CDLQI) mirrored changes in the IGA, with improvement in the mean CDLQI from 14.4 at the start of the treatment to 7.5 at the 3- to 5-month follow-up. Further improvement in the CDLQI to 6.6 in patients who continued methotrexate beyond 10 months confirmed continued improvement in disease control beyond medium-term therapy. The treatment was well tolerated. Methotrexate appears to be an effective, safe treatment for severe pediatric AD. Its therapeutic effects continue beyond the medium-term treatment period, as reflected by further improvement in IGA and CDLQI scores in patients who continued methotrexate therapy beyond 10 months.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/28730617/</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0.6116</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>28241280</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Pediatric Contact Dermatitis Registry Data on Contact Allergy in Children With Atopic Dermatitis.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Jacob SE; McGowan M; Silverberg NB; Pelletier JL; Fonacier L; Mousdicas N; Powell D; Scheman A; Goldenberg A</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>JAMA dermatology</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>10.1111/bjd.15065</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis (AD) and allergic contact dermatitis (ACD) have a dynamic relationship not yet fully understood. Investigation has been limited thus far by a paucity of data on the overlap of these disorders in pediatric patients. To use data from the Pediatric Contact Dermatitis Registry to elucidate the associations and sensitizations among patients with concomitant AD and ACD. This retrospective case review examined 1142 patch test cases of children younger than 18 years, who were registered between January 1, 2015, and December 31, 2015, by 84 health care providers (physicians, nurse practitioners, physician assistants) from across the United States. Data were gathered electronically from multidisciplinary providers within outpatient clinics throughout the United States on pediatric patients (ages 0-18 years). All participants were patch-tested to assess sensitizations to various allergens; history of AD was noted by the patch-testing providers. Primary outcomes were sensitization rates to various patch-tested allergens. A total of 1142 patients were evaluated: 189 boys (34.2%) and 363 girls (65.8%) in the AD group and 198 boys (36.1%) and 350 girls (63.9%) in the non-AD group (data on gender identification were missing for 17 patients). Compared with those without AD, patch-tested patients with AD were 1.3 years younger (10.5 vs 11.8 years; P &lt; .001) and had longer history of dermatitis (3.5 vs 1.8 years; P &lt; .001). Patch-tested patients designated as Asian or African American were more likely to have concurrent AD (odds ratio [OR], 1.92; 95% CI, 1.20-3.10; P = .008; and OR, 4.09; 95% CI, 2.70-6.20; P &lt;.001, respectively). Patients with AD with generalized distribution were the most likely to be patch tested (OR, 4.68; 95% CI, 3.50-6.30; P &lt; .001). Patients with AD had different reaction profiles than those without AD, with increased frequency of reactions to cocamidopropyl betaine, wool alcohol, lanolin, tixocortol pivalate, and parthenolide. Patients with AD were also noted to have lower frequency of reaction to methylisothiazolinone, cobalt, and potassium dichromate. Children with AD showed significant reaction patterns to allergens notable for their use in skin care preparations. This study adds to the current understanding of AD in ACD, and the continued need to investigate the interplay between these disease processes to optimize care for pediatric patients with these conditions.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/28241280/</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0.6111</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>29305764</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>The Role and Diagnosis of Allergic Contact Dermatitis in Patients with Atopic Dermatitis.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Owen JL; Vakharia PP; Silverberg JI</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>American journal of clinical dermatology</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>10.1007/s40257-017-0340-7</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Patients with atopic dermatitis (AD) have increased penetration of allergens, immune dysregulation (including shared cytokine pathways), and frequent use of emollients and topical medications, all of which may predispose toward developing allergic contact dermatitis (ACD). Recent systematic reviews have suggested that ACD is a significant clinical problem in both children and adults with AD. While this remains controversial, ACD remains an important comorbidity and potential exacerbant of AD in clinical practice. Common relevant allergens, include lanolin, neomycin, formaldehyde, sesquiterpene lactone mix, compositae mix, and fragrances that are commonly found in AD patients' personal care products. We herein review the clinical scenarios where patch testing is indicated in AD. In addition, we review the contraindications, preferred patch-testing series, pitfalls, and challenges determining the relevance of positive patch-test reactions in AD patients.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/29305764/</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0.6085</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>26149842</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>The Association Between Bathing Habits and Severity of Atopic Dermatitis in Children.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Koutroulis I; Pyle T; Kopylov D; Little A; Gaughan J; Kratimenos P</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Clinical pediatrics</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>10.1177/0009922815594346</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis is an inflammatory skin disease that frequently affects children. The current recommendations on management using lifestyle modification are highly variable, leading to confusion and uncertainty among patients. To determine current bathing behaviors and the subsequent impact on disease severity. This was an observational cross-sectional study conducted at an urban pediatric emergency department. Parents were asked to fill out a questionnaire concerning the patient's bathing habits. The results were correlated with the atopic dermatitis severity determined by the SCORAD (SCORing Atopic Dermatitis) tool. No difference between variables was found to be significant for bathing frequency, time spent bathing, or use of moisturizers. Multivariate analysis showed that atopic dermatitis severity increased with age greater than 2 years (P = .0004) and with greater bathing duration (P = .001). Atopic dermatitis severity may be associated with a longer duration of bathing. The frequency of bathing does not appear to affect atopic dermatitis severity.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/26149842/</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0.608</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>31609858</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Patch Test Results of Contact Sensitization in Children Without Atopic Dermatitis: A Single Tertiary Center Experience.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Kundak S</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Dermatitis : contact, atopic, occupational, drug</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>10.1097/DER.0000000000000530</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Allergic contact dermatitis (ACD) has become more frequent in children. The prevalence of contact sensitization varies with respect to age, sex, and geographic localization. The aim of the study was to investigate the experience of a tertiary health center regarding the patch test results of contact sensitization in children without atopic dermatitis. This is a retrospective review of 89 children (30 boys and 59 girls) who were aged between 3 and 18 years and who were diagnosed with ACD between July 2013 and July 2017. Children with a known history of atopic dermatitis were excluded. All patients were tested with the TRUE (Thin-layer Rapid Use Epicutaneous) test series. The most frequently determined allergens by TRUE test were methylchloroisothiazolinone (n = 7 [16.3%]), disperse blue 106 (n = 5 [11.6%]), and bacitracin (n = 5 [11.6%]). Formaldehyde-related allergens produced 15 positives. Preservatives, such as methylchloroisothiazolinone, formaldehyde, and formaldehyde releasers, emerge as the most frequent allergens in children who undergo patch testing because of ACD. This finding might be attributed to the increase in the utilization of these chemical compounds in personal hygiene products for children.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/31609858/</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0.6073</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>35548366</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Vegetable Butters and Oils as Therapeutically and Cosmetically Active Ingredients for Dermal Use: A Review of Clinical Studies.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Poljšak N; Kočevar Glavač N</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Frontiers in pharmacology</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>10.1146/annurev.nu.10.070190.002245</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">While the chemical composition of vegetable butters and oils has been studied in detail, there is limited knowledge about their mechanisms of action after application on the skin. To understand their dermal effects better, 27 clinical studies evaluating 17 vegetable oils (almond, argan, avocado, borage, coconut, evening primrose, kukui, marula, mustard, neem, olive, rapeseed, sacha inchi, safflower, shea butter, soybean and sunflower oils) were reviewed in this research. The reviewed studies focused on non-affected skin, infant skin, psoriasis, xerosis, UVB-induced erythema, atopic dermatitis, </t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35548366/</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>0.6072</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>39154354</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Capturing and reporting topical treatment use in childhood eczema: lessons for data collection in eczema trials.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Memory KE; MacNeill SJ; Thomas KS; Santer M; Ridd MJ</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Clinical and experimental dermatology</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>10.1093/ced/llae328</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Emollients and topical corticosteroids (TCS) prevent and treat flares in eczema. However, topical treatment use is poorly recorded and reported in clinical trials. There is no clear consensus of how best to capture and summarize topical treatment use. To explore different ways of capturing and reporting topical treatment use in childhood eczema. This was a secondary data analysis using 450 participants from the Best Emollients for Eczema (BEE) trial. Participants were allocated to use one type of emollient (lotion, cream, gel or ointment) 'twice daily and when required' for 16 weeks. Otherwise, clinical management remained unchanged. Parents completed weekly questions about topical therapy use and eczema symptoms. Two versions of topical treatment use questionnaires were used. The first (n = 202, 44.9%) asked parents to report treatment use on days 1-7, starting completion on the day they were randomized. The second (n = 248, 55.1%) reported use by day of the week (Monday to Sunday), starting completion the first Monday after randomization. Both underwent patient and public involvement review but the second version was tested more thoroughly using cognitive interviewing techniques, following parent feedback that questions on the first version were confusing. Descriptive statistics compared questionnaire completion and differences in emollient and TCS use. Overall, questionnaire completion for both emollient and TCS use decreased with time, but at weeks 1 and 16, it was 84.7% (381/450) and 58.9% (265/450) for emollient use, and 94.2% (424/450) and 80.4% (362/450) for TCS use, respectively. Fewer emollient use questionnaires were completed with the first (33.5%, 1082/3232 patient-weeks) than the second (87.9%, 3489/3968 patient-weeks) version (P &lt; 0.001). TCS use questionnaire completion were similar for both (84.9%, 2744/3232 patient-weeks and 87.4%, 3468/3968 patient-weeks, P = 0.002). We present different ways of summarizing topical treatment use. Although questionnaire completion was similar for TCS use, emollient-use data completeness was higher in the second version. When designing questionnaires, balancing the detail and complexity of questions is important, especially if being collected as a secondary outcome measure. Numerous ways of summarizing the same data can provide different information. Future collection and reporting of treatment use should reflect specific trial aims.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39154354/</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>0.6068</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>27271265</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Children with Dry Skin and Atopic Predisposition: Outcome Measurement with Validated Scores for Atopic Dermatitis.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sawatzky S; Schario M; Stroux A; Lünnemann L; Zuberbier T; Blume-Peytavi U; Garcia Bartels N</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Skin pharmacology and physiology</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>10.1159/000444590</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Dry skin is a common skin condition in childhood. Few studies exist investigating the influence of daily skin care on dry skin in infants at risk of developing atopic dermatitis (AD). We aimed to assess the effect of skin care on dry skin in this special cohort using validated scores for AD and analysis of skin microtopography. 43 children were randomized to group 1 (G1) and group 2 (G2) and 22 infants to group 3 (G3). During 16 weeks, G1 and G3 applied daily a plant-based emollient and G2 a petrolatum-based emollient. The core outcome was assessed by Severity Scoring of Atopic Dermatitis (SCORAD) and Patient-Oriented SCORing Atopic Dermatitis (PO-SCORAD). The influence on the parents' life was evaluated by a questionnaire and microtopography by Visioscan® VC 98. The SCORAD index declined significantly until week (W) 16 in all groups (p ≤ 0.041). The sleeplessness score analyzed by PO-SCORAD was highly reduced after W12 in G1 and after W16 in G2 (p ≤ 0.030). The influence on the parents' anxiety was reduced in G3 at W12 and W16 (p = 0.016). The Visioscan parameter scaliness strongly diminished at W4 (p ≤ 0.049) and W16 (p ≤ 0.013) in all groups. This trial demonstrates improved skin conditions and sleep following daily emollient application in infants and children having dry skin and being at risk of AD. Especially parents of infants showed a reduced fear that their children might develop AD. Further studies are required to investigate the preventive effect of daily emollient therapy in this special cohort evaluating the outcome measures used in this trial.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/27271265/</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0.6065</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>35887707</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Use of Dexpanthenol for Atopic Dermatitis-Benefits and Recommendations Based on Current Evidence.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Cho YS; Kim HO; Woo SM; Lee DH</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Journal of clinical medicine</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>10.1111/j.1600-0536.1998.tb05732.x</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis (AD) is an inflammatory skin disease of multiple phenotypes and endotypes, and is highly prevalent in children. Many people of all ages, including active adolescents, pregnant women, and the elderly, suffer from AD, experiencing chronicity, flares, and unexpected relapse. Dexpanthenol has multiple pharmacological effects and has been employed to treat various skin disorders such as AD. We aimed to summarize the up-to-date evidence relating to dexpanthenol and to provide a consensus on how to use dexpanthenol effectively for the treatment of AD. The evidence to date on the application and efficacy of dexpanthenol in AD was reviewed. The literature search focused on dexpanthenol use and the improvement of skin barrier function, the prevention of acute flares, and its topical corticosteroid (TCS) sparing effects. Evidence and recommendations for special groups such as pregnant women, and the effects of dexpanthenol and emollient plus in maintenance therapy, were also summarized. Dexpanthenol is effective and well-tolerated for the treatment of AD. Dexpanthenol improves skin barrier function, reduces acute and frequent flares, has a significant TCS sparing effect, and enhances wound healing for skin lesions. This review article provides helpful advice for clinicians and patients on the proper maintenance treatment of AD. Dexpanthenol, as an active ingredient in ointments or emollients, is suitable for the treatment and maintenance of AD. This paper will guide dermatologists and clinicians to consider dexpanthenol as a treatment option for mild to moderate AD.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35887707/</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0.6064000000000001</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>40256827</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Is colloidal oat an effective emollient ingredient for the prevention and treatment of atopic dermatitis in infants?</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Fowler JF; Ma L; Bergman J; Horowitz P; Lavender T; Eichenfield LF; Draelos Z; Danby SG; Cork MJ</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>The Journal of dermatological treatment</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>10.1080/09546634.2025.2487945</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Atopic dermatitis (AD) is a chronic inflammatory skin condition characterized by barrier dysfunction and immune dysregulation, often leading to increased allergen penetration, sensitization, and secondary infections. Colloidal oat emollients are widely used in adult AD management, but their role in pediatric AD treatment, prevention, and allergy modulation remains under investigation. A comprehensive literature review evaluated clinical and preclinical studies on colloidal oat-containing emollients in pediatric AD treatment and prevention. Studies assessing skin barrier function, immune modulation, AD prevention, food allergy risk, and healthcare utilization were included. Colloidal oat emollients improved skin hydration, reduced transepidermal water loss (TEWL), and supported barrier repair, leading to fewer AD flares and reduced reliance on steroid treatments. Studies suggest that early, consistent use of advanced emollient formulations may lower AD incidence in high-risk infants and reduce food sensitization rates. Real-world data indicate that patients using colloidal oat emollients have fewer clinic visits and lower overall healthcare costs. Concerns about oat sensitization remain unsubstantiated in most studies. Colloidal oat emollients are effective, well-tolerated, and cost-efficient for pediatric AD management. Their barrier-restorative and anti-inflammatory properties may reduce AD and allergy risk. Future research should focus on head-to-head emollient comparisons to optimize treatment strategies.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40256827/</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.6062</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>34743369</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Natural moisturizing factors in children with and without eczema: Associations with lifestyle and genetic factors.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Basu MN; Mortz CG; Jensen TK; Barington T; Halken S</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Journal of the European Academy of Dermatology and Venereology : JEADV</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>10.1111/jdv.17787</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Filaggrin-derived natural moisturizing factors (NMF) play an important role in skin barrier function and in atopic dermatitis (AD). Its deficiency is associated with dry skin and increased surface pH. Studies on childhood environmental exposures and associations with NMF levels are scarce. To investigate previous exposures and genetic factors and their associations with NMF levels in young children. In a case-control study nested in a prospective birth cohort (Odense Child Cohort), 169 healthy controls (HC) and 99 children with AD were included consecutively at the age of 7 years based on previous responses from questionnaires administered at 18 months, 3 years and 5 years, pertaining to past medical history, including allergy-specific questions. NMF levels were measured via a stratum corneum tape-stripping technique, genotyping for filaggrin (FLG) gene variants was performed and data on external exposures, including usage of moisturizer and topical steroids, antibiotics and early pet exposures, were obtained from questionnaires. Natural moisturizing factors levels were significantly lower in AD participants compared to HC (P &lt; 0.001). This significance persisted after stratifying for AD subgroups of present AD, current AD during the last year and previous AD (P &lt; 0.001, P = 0.039, P = 0.009 respectively). There was a significant association between NMF and FLG genotype (P = 0.016, P = 0.002 for HC, AD respectively). NMF levels were negatively correlated with early age moisturizer use (&lt;18 months, P = 0.001) in HC but not significant in AD. We found decreased levels of NMF with early moisturizer use and a genetic influence of the FLG variant on these levels. NMF was decreased in the AD subgroup with previous AD compared with HC, which could suggest the persistence of a Th</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34743369/</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0.6058</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>40126804</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Maximal Usage Trial of Tapinarof Cream 1% Once Daily in Pediatric Patients Down to 2 Years of Age with Extensive Atopic Dermatitis.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Paller AS; Hebert AA; Gonzalez ME; Butners V; Fitzgerald N; Tabolt G; Rubenstein DS; Piscitelli SC</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>American journal of clinical dermatology</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>10.1016/j.jaci.2023.12.013</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Tapinarof cream 1% is an aryl hydrocarbon receptor agonist approved by the US Food and Drug Administration to treat atopic dermatitis (AD) in patients down to age 2 years. The aim of this study was to evaluate the safety and pharmacokinetics of tapinarof cream 1% once daily (QD) in adolescents and children with extensive AD under maximal usage conditions. Patients with a validated Investigator Global Assessment scale for Atopic Dermatitis™ (vIGA-AD™) score ≥ 3 and body surface area (BSA) involvement ≥ 25% (ages 12-17 years) or ≥ 35% (ages 2-11 years) were enrolled into three age cohorts (2-6, 7-11, and 12-17 years) and received tapinarof cream 1% QD for 4 weeks. Overall, 36 patients (12 per cohort) were enrolled; mean BSA affected was 42.8% (range 26.0-90.0) and mean Eczema Area and Severity Index (EASI) score was 23.8. At baseline, 28 patients (77.8%) had a vIGA-AD™ score of 3 (moderate). No-to-minimal tapinarof systemic exposure was observed (25% of post-treatment plasma samples were below the quantifiable limit of a highly sensitive assay [&lt; 50 pg/mL]). Mean maximum plasma concentration (C Tapinarof cream exhibits highly favorable safety and pharmacokinetics in adolescents and children down to age 2 years with extensive AD. ClinicalTrials.gov: NCT05186805.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40126804/</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0.6049</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>35677673</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Contact allergens in moisturizers in preventative emollient therapy - A systematic review.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Ryczaj K; Dumycz K; Spiewak R; Feleszko W</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Clinical and translational allergy</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>10.1016/j.jaad.2020.11.002</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Results of preventative emollient therapy on atopic dermatitis and food allergy trials are inconsistent. In addition to the ingredients considered beneficial, the moisturizers may contain potentially harmful haptens. This study aimed to assess the prevalence of haptens in moisturizers used in studies to prevent atopic dermatitis or food allergy and assess their correlations to the trial results. A systematic search of studies investigating the role of emollient usage in preventing atopic dermatitis or food allergy in infants was performed from inception to December 2020. Haptens were identified based on the nine common patch test series (European, American, and Australian). 12 clinical trial studies were included in the review. In total, 16 different emollients were applied as an intervention. The vast majority (75%) of preparations contained at least one hapten from which several substances pose high allergic or irritant potential. Quantitative data synthesis of the findings regarding food allergy and atopic dermatitis prevention was not possible due to the significant heterogeneity of preparations used. Careful selection of emollient should consider the absence of potentially harmful ingredients, particularly when used in youngest children. Chronic skin exposure to haptens promotes the development of allergic contact dermatitis and moreover, via deterioration of the skin barrier and subclinical inflammation, may facilitate epicutaneous sensitization and promote atopic dermatitis; however further research is needed to validate our suppositions.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35677673/</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.6032999999999999</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>34621960</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>A new therapeutic horizon in diaper dermatitis: Novel agents with novel action.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Hebert AA</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>International journal of women's dermatology</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>10.1016/j.ijwd.2021.02.003</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>This review looks at novel combinations of topical agents (i.e., zinc gluconate, zinc oxide, dexpanthenol, and taurine) that target a combination of mechanisms in diaper dermatitis. A literature search of published studies was conducted using the search terms "diaper dermatitis", "treatment of diaper dermatitis in infants", "treatment of diaper dermatitis in adults", "nonsteroidal", "nonantibiotic", "antiinflammatory", "moisturizer", and "treatment for irritation". A total of 207 related articles were screened, and those categorized as clinical trials and reviews were studied and compared. Articles with common themes were categorized, summarized, and presented herein. Diaper dermatitis, also referred to as diaper rash, napkin dermatitis, and nappy rash, is the most common skin eruption in infants and toddlers. In the last several years, there have been several technologic advances in diaper design to lessen the severity of diaper dermatitis symptoms. However, due to the unique environment of the diaper area, children and adults continue to have recurring symptoms of diaper dermatitis. Both commercially available products and certain home remedies are considered effective for managing sensitive and delicate skin in the diaper area. These topical agents create a protective barrier over the skin and reduce the impact of external irritants, which cause the reddening and burning sensation often associated with diaper dermatitis. A range of therapeutic strategies for preventing and controlling diaper dermatitis are summarized in this manuscript.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34621960/</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.6029</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PubMed</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>37278500</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Algorithm to attenuate atopic dermatitis and for promoting a healthy skin barrier using skincare in newborns and infants.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Schachner LA; Blume-Peytavi U; Andriessen A; Izakovic J; Maruani A; Micali G; Murashkin N; Salavastru C; Torrelo A</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Italian journal of dermatology and venereology</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>10.23736/S2784-8671.23.07336-X</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>The human skin barrier is structurally and functionally immature at birth, with elevated skin surface pH, lower lipid content, and lower resistance to chemicals and pathogens. Infants at risk for atopic dermatitis (AD) may present with xerosis almost immediately after birth. The current algorithm on skincare for newborns and infants aims to promote a healthy skin barrier and potential mitigation of AD. The project used a modified Delphi hybrid process comprising face-to-face discussions followed by an online follow-up replacing a questionnaire. During the meeting, a panel of eight clinicians who treat newborns and infants discussed the systematic literature review results and a draft algorithm addressing non-prescription skincare for neonates and infants. Online the panel reviewed and adopted the algorithm using evidence coupled with the panel's expert opinion and clinical experience. The algorithm provides clinical information for pediatric dermatologists, dermatologists, and pediatric healthcare providers treating neonates and infants. The advisors adopted a scale based on clinical signs for the algorithm: 1) scaling/xerosis; 2) erythema; and 3) erosion/oozing. Skincare for newborns and infants includes: aim for a cool environment and soft cotton clothing, give lukewarm baths (~5 min, 2-3 x week) with consideration of a gentle cleanser (pH 4-6) and the application of a full-body moisturizing after bath, while avoiding products with toxic and irritating ingredients. A growing body of evidence recognizes the benefits of ongoing daily use of non-alkaline cleansers and moisturizers. Gentle cleansers and moisturizers containing barrier lipids help maintain the protective skin barrier when applied from birth onwards.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37278500/</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0.6018</v>
       </c>
     </row>
   </sheetData>
